--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S110"/>
+  <dimension ref="A1:S111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,34 +938,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one_from_file specimen_label_allocation.csv</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_note</t>
+          <t>q0_label_range</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ƙungiya: ${enum_team}  |  LGA: ${enum_lga}</t>
+          <t>Tabbatar da littafin lakabin ƙungiyar ka</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Team: ${enum_team}  |  LGA: ${enum_lga}</t>
+          <t>Confirm the specimen label book issued to your team</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>team_code=${enum_team}</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -975,16 +987,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>s0_login_end</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>team_note</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ƙungiya: ${enum_team}  |  LGA: ${enum_lga}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Team: ${enum_team}  |  LGA: ${enum_lga}</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1004,24 +1024,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>s1_identification</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sashe 1: Bayanin gida</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Section 1: Household identification</t>
-        </is>
-      </c>
+          <t>s0_login_end</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1041,16 +1053,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>q1_01_state</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>s1_identification</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sashe 1: Bayanin gida</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Section 1: Household identification</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1058,11 +1078,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>'BAN'</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1074,48 +1090,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one_from_file lgas.csv</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>q1_02_lga</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Karamar hukuma</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.02 Local Government Area</t>
-        </is>
-      </c>
+          <t>q1_01_state</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>. = ${enum_lga} or ${enum_role} != 'Enumerator'</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Ba a ba ka wannan karamar hukuma ba.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>This LGA is not the one assigned to you. Check with your supervisor.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>'BAN'</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1127,22 +1123,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_from_file wards.csv</t>
+          <t>select_one_from_file lgas.csv</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>q1_03_ward</t>
+          <t>q1_02_lga</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gunduma</t>
+          <t>Karamar hukuma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.03 Ward</t>
+          <t>1.02 Local Government Area</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1153,20 +1149,24 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>. = ${enum_lga} or ${enum_role} != 'Enumerator'</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Ba a ba ka wannan karamar hukuma ba.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>This LGA is not the one assigned to you. Check with your supervisor.</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lga_code=${q1_02_lga}</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -1176,22 +1176,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_from_file settlements.csv</t>
+          <t>select_one_from_file wards.csv</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>q1_04_settlement</t>
+          <t>q1_03_ward</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ƙauye / unguwa</t>
+          <t>Gunduma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.04 Settlement</t>
+          <t>1.03 Ward</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ward_code=${q1_03_ward}</t>
+          <t>lga_code=${q1_02_lga}</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1225,22 +1225,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one_from_file settlements.csv</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>q1_05_alt_name_yn</t>
+          <t>q1_04_settlement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ana kiran wannan wuri da wani suna daban?</t>
+          <t>Ƙauye / unguwa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.05 Is the settlement known locally by a different name?</t>
+          <t>1.04 Settlement</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1255,8 +1255,16 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ward_code=${q1_03_ward}</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1266,22 +1274,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>q1_05_alt_name</t>
+          <t>q1_05_alt_name_yn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rubuta sunan da ake amfani da shi a nan</t>
+          <t>Ana kiran wannan wuri da wani suna daban?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.05 Local name</t>
+          <t>1.05 Is the settlement known locally by a different name?</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1291,11 +1299,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>${q1_05_alt_name_yn} = '1'</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1311,22 +1315,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>q1_06_structure</t>
+          <t>q1_05_alt_name</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lambar gini da aka rubuta a gidan</t>
+          <t>Rubuta sunan da ake amfani da shi a nan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.06 Structure number painted on the dwelling</t>
+          <t>1.05 Local name</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1336,22 +1340,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 999</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Lamba tsakanin 1 zuwa 999.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Enter a number between 1 and 999.</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>${q1_05_alt_name_yn} = '1'</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1369,17 +1365,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>q1_07_hh_serial</t>
+          <t>q1_06_structure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lambar gida a cikin ƙauyen</t>
+          <t>Lambar gini da aka rubuta a gidan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.07 Household serial number within the settlement</t>
+          <t>1.06 Structure number painted on the dwelling</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1417,22 +1413,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>q1_10_visit_date</t>
+          <t>q1_07_hh_serial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ranar ziyara</t>
+          <t>Lambar gida a cikin ƙauyen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.10 Date of visit</t>
+          <t>1.07 Household serial number within the settlement</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1445,17 +1441,17 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>. &gt;= date('2026-06-01') and . &lt;= date('2026-06-30')</t>
+          <t>. &gt;= 1 and . &lt;= 999</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ranar dole ta kasance tsakanin 1 zuwa 30 ga Yuni 2026.</t>
+          <t>Lamba tsakanin 1 zuwa 999.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Date must fall within the fieldwork window, 1-30 June 2026.</t>
+          <t>Enter a number between 1 and 999.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1464,32 +1460,28 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>today()</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>q1_11_gps</t>
+          <t>q1_10_visit_date</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ɗauki wurin GPS a ƙofar gidan</t>
+          <t>Ranar ziyara</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.11 GPS reading at the entrance to the dwelling</t>
+          <t>1.10 Date of visit</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1500,37 +1492,53 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>. &gt;= date('2026-06-01') and . &lt;= date('2026-06-30')</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Ranar dole ta kasance tsakanin 1 zuwa 30 ga Yuni 2026.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Date must fall within the fieldwork window, 1-30 June 2026.</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>today()</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>q1_12_prev_round</t>
+          <t>q1_11_gps</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>An ziyarci wannan gida a watan Oktoba 2025?</t>
+          <t>Ɗauki wurin GPS a ƙofar gidan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.12 Was this household visited during the October 2025 round?</t>
+          <t>1.11 GPS reading at the entrance to the dwelling</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1556,22 +1564,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one_from_file previous_round_households.csv</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>q1_13_prev_id</t>
+          <t>q1_12_prev_round</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lambar gidan da aka ba shi a 2025</t>
+          <t>An ziyarci wannan gida a watan Oktoba 2025?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.13 Household identifier allocated in the October 2025 round</t>
+          <t>1.12 Was this household visited during the October 2025 round?</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1581,25 +1589,13 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>${q1_12_prev_round} = '1'</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>settlement_id=${q1_04_settlement}</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -1609,22 +1605,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one result_of_visit</t>
+          <t>select_one_from_file previous_round_households.csv</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>q1_14_result</t>
+          <t>q1_13_prev_id</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sakamakon ziyarar</t>
+          <t>Lambar gidan da aka ba shi a 2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.14 Result of visit</t>
+          <t>1.13 Household identifier allocated in the October 2025 round</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1634,13 +1630,25 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>${q1_12_prev_round} = '1'</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>settlement_id=${q1_04_settlement}</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -1650,32 +1658,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one result_of_visit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>q1_14_stop_note</t>
+          <t>q1_14_result</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kada ka ci gaba. Sa hannu a 7.03 sannan ka mika wa mai kula da kai.</t>
+          <t>Sakamakon ziyarar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Do not complete any further section. Sign at 7.03 and hand the form to your supervisor.</t>
+          <t>1.14 Result of visit</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>${q1_14_result} != '1'</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1691,20 +1699,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>s1_end</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>q1_14_stop_note</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Kada ka ci gaba. Sa hannu a 7.03 sannan ka mika wa mai kula da kai.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Do not complete any further section. Sign at 7.03 and hand the form to your supervisor.</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>${q1_14_result} != '1'</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1720,32 +1740,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>s2_consent</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Sashe 2: Yarda</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Section 2: Consent</t>
-        </is>
-      </c>
+          <t>s1_end</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1'</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1761,47 +1769,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>q2_01_statement_read</t>
+          <t>s2_consent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>An karanta sanarwar yarda gaba ɗaya ga mai amsa?</t>
+          <t>Sashe 2: Yarda</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.01 Consent statement read aloud to the respondent in full?</t>
+          <t>Section 2: Consent</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>. = '1'</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Dole ne a karanta sanarwar yarda gaba ɗaya kafin a ci gaba.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>The consent statement must be read in full before continuing. Read it now, then record Yes.</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1'</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -1814,22 +1810,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one consent</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>q2_02_consent</t>
+          <t>q2_01_statement_read</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mai amsa ya yarda da tambayoyin?</t>
+          <t>An karanta sanarwar yarda gaba ɗaya ga mai amsa?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.02 Does the respondent consent to the household interview?</t>
+          <t>2.01 Consent statement read aloud to the respondent in full?</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1840,9 +1836,21 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>. = '1'</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Dole ne a karanta sanarwar yarda gaba ɗaya kafin a ci gaba.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>The consent statement must be read in full before continuing. Read it now, then record Yes.</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -1855,22 +1863,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one relationship</t>
+          <t>select_one consent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>q2_03_relationship</t>
+          <t>q2_02_consent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alaƙar mai amsa da shugaban gida</t>
+          <t>Mai amsa ya yarda da tambayoyin?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.03 Relationship of the respondent to the head of household</t>
+          <t>2.02 Does the respondent consent to the household interview?</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1880,11 +1888,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -1900,20 +1904,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one relationship</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>s2_end</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>q2_03_relationship</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alaƙar mai amsa da shugaban gida</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2.03 Relationship of the respondent to the head of household</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1929,32 +1949,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>s3_roster</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Sashe 3: Jerin mazauna gida</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Section 3: Household roster</t>
-        </is>
-      </c>
+          <t>s2_end</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -1970,47 +1978,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>q3_01_hh_size</t>
+          <t>s3_roster</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mutane nawa ne ke zama a wannan gida?</t>
+          <t>Sashe 3: Jerin mazauna gida</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.01 How many people usually live in this household?</t>
+          <t>Section 3: Household roster</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 40</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Adadi tsakanin 1 zuwa 40. Idan ya fi haka, sanar da mai kula da kai.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Enter between 1 and 40. If larger, notify your supervisor.</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -2023,40 +2019,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>roster</t>
+          <t>q3_01_hh_size</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mazaunin gida</t>
+          <t>Mutane nawa ne ke zama a wannan gida?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Resident</t>
+          <t>3.01 How many people usually live in this household?</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 40</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Adadi tsakanin 1 zuwa 40. Idan ya fi haka, sanar da mai kula da kai.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Enter between 1 and 40. If larger, notify your supervisor.</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>${q3_01_hh_size}</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -2064,16 +2072,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>line_no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>roster</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mazaunin gida</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Resident</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -2081,15 +2097,15 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>position(..)</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>${q3_01_hh_size}</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2097,24 +2113,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>line_note</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Layi ${line_no}</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Line ${line_no}</t>
-        </is>
-      </c>
+          <t>line_no</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -2122,7 +2130,11 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>position(..)</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -2134,39 +2146,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>r_initials</t>
+          <t>line_note</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baƙaƙen farko na suna</t>
+          <t>Layi ${line_no}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(2) Initials</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Baƙaƙen farko kawai, ba cikakken suna ba.</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Initials only - do not record the full name.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Line ${line_no}</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -2183,26 +2183,34 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one relationship</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>r_relationship</t>
+          <t>r_initials</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alaƙa da shugaban gida</t>
+          <t>Baƙaƙen farko na suna</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(3) Relationship to head</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+          <t>(2) Initials</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Baƙaƙen farko kawai, ba cikakken suna ba.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Initials only - do not record the full name.</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2224,22 +2232,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>select_one relationship</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>r_sex</t>
+          <t>r_relationship</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jinsi</t>
+          <t>Alaƙa da shugaban gida</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(4) Sex</t>
+          <t>(3) Relationship to head</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2265,34 +2273,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_one age_unit</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>r_age_unit</t>
+          <t>r_sex</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shekaru ko watanni?</t>
+          <t>Jinsi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Age recorded in years or months?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Watanni ga yara ƙasa da shekara 5.</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Months for children under 5 years.</t>
-        </is>
-      </c>
+          <t>(4) Sex</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2314,51 +2314,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one age_unit</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>r_age_years</t>
+          <t>r_age_unit</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shekaru cikakku</t>
+          <t>Shekaru ko watanni?</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(5) Age in completed years</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+          <t>Age recorded in years or months?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Watanni ga yara ƙasa da shekara 5.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Months for children under 5 years.</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>${r_age_unit} = 'years'</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>. &gt;= 5 and . &lt;= 120</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Shekaru 5 zuwa 120. Ga yara ƙasa da 5, yi amfani da watanni.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>5 to 120 years. For children under 5, record months instead.</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -2376,17 +2368,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>r_age_months</t>
+          <t>r_age_years</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Watanni cikakku</t>
+          <t>Shekaru cikakku</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(6) Age in completed months</t>
+          <t>(5) Age in completed years</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2398,22 +2390,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>${r_age_unit} = 'months'</t>
+          <t>${r_age_unit} = 'years'</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 59</t>
+          <t>. &gt;= 5 and . &lt;= 120</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Watanni 0 zuwa 59. Idan ya kai watanni 60, yi amfani da shekaru.</t>
+          <t>Shekaru 5 zuwa 120. Ga yara ƙasa da 5, yi amfani da watanni.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0 to 59 months. At 60 months and above, record age in years.</t>
+          <t>5 to 120 years. For children under 5, record months instead.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -2428,28 +2420,52 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>r_eligible</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+          <t>r_age_months</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Watanni cikakku</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>(6) Age in completed months</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>if(${r_age_unit} = 'months' and ${r_age_months} &gt;= 9 and ${r_age_months} &lt;= 59, 1, 0)</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>${r_age_unit} = 'months'</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 59</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Watanni 0 zuwa 59. Idan ya kai watanni 60, yi amfani da shekaru.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0 to 59 months. At 60 months and above, record age in years.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -2461,12 +2477,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>roster_end</t>
+          <t>r_eligible</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2478,7 +2494,11 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>if(${r_age_unit} = 'months' and ${r_age_months} &gt;= 9 and ${r_age_months} &lt;= 59, 1, 0)</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -2490,12 +2510,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>roster_count</t>
+          <t>roster_end</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2507,11 +2527,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>count(${roster})</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -2528,7 +2544,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>q3_02_eligible</t>
+          <t>roster_count</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -2542,7 +2558,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>sum(${r_eligible})</t>
+          <t>count(${roster})</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -2556,36 +2572,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>roster_mismatch_note</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>⚠ Ka ce mutane ${q3_01_hh_size} ne, amma ka rubuta ${roster_count}. Duba kafin ka ci gaba.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>⚠ You recorded ${q3_01_hh_size} usual residents but listed ${roster_count}. Check the roster before continuing.</t>
-        </is>
-      </c>
+          <t>q3_02_eligible</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>${roster_count} != ${q3_01_hh_size}</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>sum(${r_eligible})</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -2602,23 +2610,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>q3_02_note</t>
+          <t>roster_mismatch_note</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yara masu watanni 9-59 a wannan gida: ${q3_02_eligible}</t>
+          <t>⚠ Ka ce mutane ${q3_01_hh_size} ne, amma ka rubuta ${roster_count}. Duba kafin ka ci gaba.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.02 Children aged 9-59 completed months in this household: ${q3_02_eligible}</t>
+          <t>⚠ You recorded ${q3_01_hh_size} usual residents but listed ${roster_count}. Check the roster before continuing.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>${roster_count} != ${q3_01_hh_size}</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -2634,16 +2646,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>s3_end</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>q3_02_note</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Yara masu watanni 9-59 a wannan gida: ${q3_02_eligible}</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.02 Children aged 9-59 completed months in this household: ${q3_02_eligible}</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
@@ -2663,32 +2683,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Yaro</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Child</t>
-        </is>
-      </c>
+          <t>s3_end</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1' and ${q3_02_eligible} &gt; 0</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -2696,11 +2704,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>${q3_02_eligible}</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -2708,32 +2712,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>child_index</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Yaro</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1' and ${q3_02_eligible} &gt; 0</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>position(..)</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>${q3_02_eligible}</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -2741,48 +2757,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>q4_01_line</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Layin yaron a jerin mazauna</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>4.01 Line number of this child in the Section 3 roster</t>
-        </is>
-      </c>
+          <t>child_index</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>position(..)</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -2794,28 +2790,48 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>q4_02_initials</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>q4_01_line</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Layin yaron a jerin mazauna</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4.01 Line number of this child in the Section 3 roster</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>indexed-repeat(${r_initials}, ${roster}, ${q4_01_line})</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -2832,7 +2848,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>q4_03_age_months</t>
+          <t>q4_02_initials</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2846,7 +2862,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>indexed-repeat(${r_age_months}, ${roster}, ${q4_01_line})</t>
+          <t>indexed-repeat(${r_initials}, ${roster}, ${q4_01_line})</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -2860,24 +2876,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>child_age_note</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Watanni: ${q4_03_age_months}</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>4.03 Age in completed months (from roster): ${q4_03_age_months}</t>
-        </is>
-      </c>
+          <t>q4_03_age_months</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -2885,7 +2893,11 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>indexed-repeat(${r_age_months}, ${roster}, ${q4_01_line})</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
@@ -2897,31 +2909,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>q4_04_sex</t>
+          <t>child_age_note</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jinsin yaron</t>
+          <t>Watanni: ${q4_03_age_months}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.04 Sex of the child</t>
+          <t>4.03 Age in completed months (from roster): ${q4_03_age_months}</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -2938,22 +2946,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one measured</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>q4_05_weight_status</t>
+          <t>q4_04_sex</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>An auna nauyin yaron?</t>
+          <t>Jinsin yaron</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.05 Was the child weighed?</t>
+          <t>4.04 Sex of the child</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2979,22 +2987,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one measured</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>q4_05_weight_kg</t>
+          <t>q4_05_weight_status</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nauyi (kg)</t>
+          <t>An auna nauyin yaron?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.05 Weight in kg</t>
+          <t>4.05 Was the child weighed?</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3004,26 +3012,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>${q4_05_weight_status} = 'measured'</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>. &gt;= 2.0 and . &lt;= 30.0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Nauyi tsakanin 2.0 zuwa 30.0 kg.</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Weight must be between 2.0 and 30.0 kg for a child aged 9-59 months.</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -3036,22 +3028,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>select_one measured</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>q4_06_height_status</t>
+          <t>q4_05_weight_kg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>An auna tsayin yaron?</t>
+          <t>Nauyi (kg)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4.06 Was the child measured?</t>
+          <t>4.05 Weight in kg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3061,10 +3053,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>${q4_05_weight_status} = 'measured'</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>. &gt;= 2.0 and . &lt;= 30.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Nauyi tsakanin 2.0 zuwa 30.0 kg.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Weight must be between 2.0 and 30.0 kg for a child aged 9-59 months.</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -3077,22 +3085,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one measured</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>q4_06_height_cm</t>
+          <t>q4_06_height_status</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tsayi (cm)</t>
+          <t>An auna tsayin yaron?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.06 Length or height in cm</t>
+          <t>4.06 Was the child measured?</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3102,26 +3110,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>${q4_06_height_status} = 'measured'</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -3134,22 +3126,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>select_one measure_position</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>q4_07_position</t>
+          <t>q4_06_height_cm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yadda aka auna yaron</t>
+          <t>Tsayi (cm)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.07 Position in which the child was measured</t>
+          <t>4.06 Length or height in cm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3164,9 +3156,21 @@
           <t>${q4_06_height_status} = 'measured'</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -3179,30 +3183,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one measure_position</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>q4_07_position_warn</t>
+          <t>q4_07_position</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
+          <t>Yadda aka auna yaron</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
+          <t>4.07 Position in which the child was measured</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
+          <t>${q4_06_height_status} = 'measured'</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3220,32 +3228,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>select_one card_seen</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>q4_08_card</t>
+          <t>q4_07_position_warn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Za a iya ganin katin rigakafi na yaron?</t>
+          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.08 May I see the child's vaccination card or health record?</t>
+          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3261,32 +3269,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>select_one document_type</t>
+          <t>select_one card_seen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>q4_08a_doc_type</t>
+          <t>q4_08_card</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wane irin takarda aka gani?</t>
+          <t>Za a iya ganin katin rigakafi na yaron?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
+          <t>4.08 May I see the child's vaccination card or health record?</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>${q4_08_card} = '1'</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3302,31 +3310,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one document_type</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q4_09_measles_card</t>
+          <t>q4_08a_doc_type</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>An rubuta allurar kyanda a katin?</t>
+          <t>Wane irin takarda aka gani?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.09 Copy from the card: is a measles dose recorded?</t>
+          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>${q4_08_card} = '1'</t>
@@ -3347,22 +3351,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q4_10_measles_recall</t>
+          <t>q4_09_measles_card</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>An taɓa yi wa yaron allurar kyanda?</t>
+          <t>An rubuta allurar kyanda a katin?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.10 Has this child ever received a measles vaccination?</t>
+          <t>4.09 Copy from the card: is a measles dose recorded?</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>${q4_08_card} = '2'</t>
+          <t>${q4_08_card} = '1'</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3397,17 +3401,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>q4_11_diarrhoea</t>
+          <t>q4_10_measles_recall</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
+          <t>An taɓa yi wa yaron allurar kyanda?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
+          <t>4.10 Has this child ever received a measles vaccination?</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3417,7 +3421,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>${q4_08_card} = '2'</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3438,17 +3446,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q4_12_antibiotic</t>
+          <t>q4_11_diarrhoea</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
+          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
+          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3479,17 +3487,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q4_12a_more_than_one</t>
+          <t>q4_12_antibiotic</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>An sha fiye da magani ɗaya?</t>
+          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
+          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3499,11 +3507,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>${q4_12_antibiotic} = '1'</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -3519,27 +3523,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q4_13_placeholder_warning</t>
+          <t>q4_12a_more_than_one</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
+          <t>An sha fiye da magani ɗaya?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
+          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>${q4_12_antibiotic} = '1'</t>
@@ -3560,31 +3568,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>select_one_from_file medicines.csv</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q4_13_medicine</t>
+          <t>q4_13_placeholder_warning</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wane magani aka sha?</t>
+          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4.13 Which antibiotic was taken?</t>
+          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>${q4_12_antibiotic} = '1'</t>
@@ -3595,11 +3599,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
@@ -3609,22 +3609,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file medicines.csv</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q4_14_medicine_other</t>
+          <t>q4_13_medicine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
+          <t>Wane magani aka sha?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.14 Write the name of the medicine as reported</t>
+          <t>4.13 Which antibiotic was taken?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>${q4_13_medicine} = 'OTHER96'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3644,7 +3644,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
@@ -3654,22 +3658,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>q4_15_no_prescription</t>
+          <t>q4_14_medicine_other</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>An sami maganin ba tare da takardar likita ba?</t>
+          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
+          <t>4.14 Write the name of the medicine as reported</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3681,7 +3685,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>${q4_12_antibiotic} = '1'</t>
+          <t>${q4_13_medicine} = 'OTHER96'</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3699,22 +3703,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one photo_taken</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q4_16_photo_status</t>
+          <t>q4_15_no_prescription</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>An ɗauki hoton kunshin maganin?</t>
+          <t>An sami maganin ba tare da takardar likita ba?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4.16 Was a photograph of the medicine packaging taken?</t>
+          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3744,22 +3748,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one photo_taken</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q4_16_photo</t>
+          <t>q4_16_photo_status</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ɗauki hoton kunshin maganin</t>
+          <t>An ɗauki hoton kunshin maganin?</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4.16 Photograph of the medicine packaging</t>
+          <t>4.16 Was a photograph of the medicine packaging taken?</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3771,7 +3775,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>${q4_16_photo_status} = '1'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3780,11 +3784,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>max-pixels=1024</t>
-        </is>
-      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -3793,35 +3793,47 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>s5_specimen</t>
+          <t>q4_16_photo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sashe 5: Tattara samfuri</t>
+          <t>Ɗauki hoton kunshin maganin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Section 5: Specimen collection</t>
+          <t>4.16 Photograph of the medicine packaging</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>${q4_16_photo_status} = '1'</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>max-pixels=1024</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -3830,16 +3842,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>q5_01_specimen_eligible</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+          <t>s5_specimen</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sashe 5: Tattara samfuri</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Section 5: Specimen collection</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
@@ -3847,11 +3867,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -3863,36 +3879,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q5_01_note</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
-        </is>
-      </c>
+          <t>q5_01_specimen_eligible</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>${q5_01_specimen_eligible} = 0</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -3904,34 +3912,30 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>q5_02_specimen_obtained</t>
+          <t>q5_01_note</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>An sami samfurin bayan gida daga yaron?</t>
+          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.02 Was a stool specimen obtained from this child?</t>
+          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>${q5_01_specimen_eligible} = 1</t>
+          <t>${q5_01_specimen_eligible} = 0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3949,22 +3953,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>q5_03_label_serial</t>
+          <t>q5_02_specimen_obtained</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lambar lakabin samfuri (lamba 6)</t>
+          <t>An sami samfurin bayan gida daga yaron?</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
+          <t>5.02 Was a stool specimen obtained from this child?</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3976,31 +3980,15 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end)</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Lambar ba ta cikin kewayon ƙungiyar ka ba. Duba lakabin.</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Serial is not within the range allocated to your team. Check the label.</t>
-        </is>
-      </c>
+          <t>${q5_01_specimen_eligible} = 1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>numbers</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
@@ -4010,30 +3998,58 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>check_digit_expected</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+          <t>q5_03_label_serial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Lambar lakabin samfuri (lamba 6)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Lambar ba ta cikin kewayon ƙungiyar ka ba. Duba lakabin.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Serial is not within the range allocated to your team. Check the label.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>numbers</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
@@ -4043,52 +4059,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>q5_03_check_digit</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Lambar tantancewa (bayan layin)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>5.03 Check character (after the hyphen)</t>
-        </is>
-      </c>
+          <t>check_digit_expected</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -4100,28 +4092,52 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>specimen_label_full</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+          <t>q5_03_check_digit</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Lambar tantancewa (bayan layin)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>5.03 Check character (after the hyphen)</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -4133,40 +4149,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>q5_04_coldbox_time</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>5.04 Time the specimen was placed in the cold box</t>
-        </is>
-      </c>
+          <t>specimen_label_full</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
@@ -4178,22 +4182,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>q5_05_coldbox_temp</t>
+          <t>q5_04_coldbox_time</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Zafin akwatin sanyi (°C)</t>
+          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5.05 Temperature shown on the cold box thermometer</t>
+          <t>5.04 Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4208,21 +4212,9 @@
           <t>${q5_02_specimen_obtained} = '1'</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Temperature must be between -20.0 and 40.0 °C.</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
@@ -4235,35 +4227,51 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>q5_05_temp_warn</t>
+          <t>q5_05_coldbox_temp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
+          <t>Zafin akwatin sanyi (°C)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
+          <t>5.05 Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Temperature must be between -20.0 and 40.0 °C.</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -4276,34 +4284,30 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>select_one no_specimen_reason</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>q5_06_reason</t>
+          <t>q5_05_temp_warn</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dalilin da ya sa ba a sami samfuri ba</t>
+          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5.06 Reason no specimen was obtained</t>
+          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '2'</t>
+          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4321,22 +4325,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one no_specimen_reason</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q5_07_reason_other</t>
+          <t>q5_06_reason</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bayyana dalilin</t>
+          <t>Dalilin da ya sa ba a sami samfuri ba</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5.07 Specify</t>
+          <t>5.06 Reason no specimen was obtained</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4348,7 +4352,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>${q5_06_reason} = '96'</t>
+          <t>${q5_02_specimen_obtained} = '2'</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4366,20 +4370,36 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>s5_end</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+          <t>q5_07_reason_other</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bayyana dalilin</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5.07 Specify</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>${q5_06_reason} = '96'</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -4395,12 +4415,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>child_end</t>
+          <t>s5_end</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -4424,32 +4444,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>s6_environment</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Sashe 6: Yanayin gida</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Section 6: Household environment</t>
-        </is>
-      </c>
+          <t>child_end</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4465,32 +4473,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>select_one water_source</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>q6_01_water</t>
+          <t>s6_environment</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
+          <t>Sashe 6: Yanayin gida</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6.01 What is the main source of drinking water for this household?</t>
+          <t>Section 6: Household environment</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4506,22 +4514,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>select_one water_source</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>q6_02_toilet</t>
+          <t>q6_01_water</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
+          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6.02 What kind of toilet facility do members of this household use?</t>
+          <t>6.01 What is the main source of drinking water for this household?</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -4547,22 +4555,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>q6_03_livestock</t>
+          <t>q6_02_toilet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
+          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
+          <t>6.02 What kind of toilet facility do members of this household use?</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4588,22 +4596,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>q6_04_animal_antibiotic</t>
+          <t>q6_03_livestock</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
+          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4613,11 +4621,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>${q6_03_livestock} = '1'</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4633,22 +4637,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one handwashing</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>q6_05_handwashing</t>
+          <t>q6_04_animal_antibiotic</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
+          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
+          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4658,7 +4662,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>${q6_03_livestock} = '1'</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4674,22 +4682,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one handwashing</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>q6_06_hh_diarrhoea</t>
+          <t>q6_05_handwashing</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
+          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4715,22 +4723,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_multiple assets</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>q6_07_assets</t>
+          <t>q6_06_hh_diarrhoea</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6.07 Which of the following does this household own?</t>
+          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4741,21 +4749,9 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be selected together with any other item.</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
@@ -4768,23 +4764,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_multiple assets</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>s6_end</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+          <t>q6_07_assets</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>6.07 Which of the following does this household own?</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be selected together with any other item.</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -4797,24 +4817,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>s7_closeout</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Sashe 7: Kammalawa</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Section 7: Close-out and supervisor review</t>
-        </is>
-      </c>
+          <t>s6_end</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
@@ -4834,16 +4846,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>interview_duration_min</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+          <t>s7_closeout</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sashe 7: Kammalawa</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Section 7: Close-out and supervisor review</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
@@ -4851,11 +4871,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
@@ -4867,24 +4883,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>q7_02_observation</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Duk wani abin lura da zai taimaka wa ofis</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>7.02 Record any observation that may help the office interpret this form</t>
-        </is>
-      </c>
+          <t>interview_duration_min</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
@@ -4892,13 +4900,13 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
@@ -4908,22 +4916,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>select_one_from_file staff_roster.csv</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>q7_04_supervisor</t>
+          <t>q7_02_observation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lambar mai kula</t>
+          <t>Duk wani abin lura da zai taimaka wa ofis</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7.04 Supervisor code</t>
+          <t>7.02 Record any observation that may help the office interpret this form</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4934,14 +4942,10 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>role='Team supervisor'</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>autocomplete</t>
+          <t>multiline</t>
         </is>
       </c>
       <c r="O108" t="inlineStr"/>
@@ -4953,38 +4957,42 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>select_one supervisor_decision</t>
+          <t>select_one_from_file staff_roster.csv</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>q7_05_supervisor_decision</t>
+          <t>q7_04_supervisor</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Shawarar mai kula kan wannan takarda</t>
+          <t>Lambar mai kula</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.05 Supervisor decision on this form</t>
+          <t>7.04 Supervisor code</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>${q7_04_supervisor} != ''</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>role='Team supervisor'</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
@@ -4994,20 +5002,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one supervisor_decision</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>s7_end</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+          <t>q7_05_supervisor_decision</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Shawarar mai kula kan wannan takarda</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>7.05 Supervisor decision on this form</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>${q7_04_supervisor} != ''</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5019,6 +5039,35 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>s7_end</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S111"/>
+  <dimension ref="A1:S113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,32 +3085,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>select_one measured</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>q4_06_height_status</t>
+          <t>weight_implausible_warn</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>An auna tsayin yaron?</t>
+          <t>⚠ Wannan nauyin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.06 Was the child measured?</t>
+          <t>⚠ This weight is outside the usual range for a child aged ${q4_03_age_months} months. Re-weigh to confirm, then record what you measure.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>${q4_05_weight_status} = 'measured' and (${q4_05_weight_kg} &lt; 5.0 or ${q4_05_weight_kg} &gt; 28.0)</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3126,22 +3126,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one measured</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>q4_06_height_cm</t>
+          <t>q4_06_height_status</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tsayi (cm)</t>
+          <t>An auna tsayin yaron?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.06 Length or height in cm</t>
+          <t>4.06 Was the child measured?</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3151,26 +3151,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>${q4_06_height_status} = 'measured'</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -3183,22 +3167,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>select_one measure_position</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>q4_07_position</t>
+          <t>q4_06_height_cm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yadda aka auna yaron</t>
+          <t>Tsayi (cm)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.07 Position in which the child was measured</t>
+          <t>4.06 Length or height in cm</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3213,9 +3197,21 @@
           <t>${q4_06_height_status} = 'measured'</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3233,17 +3229,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>q4_07_position_warn</t>
+          <t>height_implausible_warn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
+          <t>⚠ Wannan tsayin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
+          <t>⚠ This height is outside the usual range for a child aged ${q4_03_age_months} months. Re-measure to confirm, then record what you measure.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3251,7 +3247,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
+          <t>${q4_06_height_status} = 'measured' and (${q4_06_height_cm} &lt; 60.0 or ${q4_06_height_cm} &gt; 125.0)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3269,22 +3265,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>select_one card_seen</t>
+          <t>select_one measure_position</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>q4_08_card</t>
+          <t>q4_07_position</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Za a iya ganin katin rigakafi na yaron?</t>
+          <t>Yadda aka auna yaron</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.08 May I see the child's vaccination card or health record?</t>
+          <t>4.07 Position in which the child was measured</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3294,7 +3290,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>${q4_06_height_status} = 'measured'</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3310,22 +3310,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one document_type</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q4_08a_doc_type</t>
+          <t>q4_07_position_warn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wane irin takarda aka gani?</t>
+          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
+          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>${q4_08_card} = '1'</t>
+          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3351,22 +3351,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one card_seen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q4_09_measles_card</t>
+          <t>q4_08_card</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>An rubuta allurar kyanda a katin?</t>
+          <t>Za a iya ganin katin rigakafi na yaron?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.09 Copy from the card: is a measles dose recorded?</t>
+          <t>4.08 May I see the child's vaccination card or health record?</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3376,11 +3376,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>${q4_08_card} = '1'</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3396,34 +3392,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one document_type</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>q4_10_measles_recall</t>
+          <t>q4_08a_doc_type</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>An taɓa yi wa yaron allurar kyanda?</t>
+          <t>Wane irin takarda aka gani?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4.10 Has this child ever received a measles vaccination?</t>
+          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>${q4_08_card} = '2'</t>
+          <t>${q4_08_card} = '1'</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3441,22 +3433,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q4_11_diarrhoea</t>
+          <t>q4_09_measles_card</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
+          <t>An rubuta allurar kyanda a katin?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
+          <t>4.09 Copy from the card: is a measles dose recorded?</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3466,7 +3458,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>${q4_08_card} = '1'</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -3487,17 +3483,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q4_12_antibiotic</t>
+          <t>q4_10_measles_recall</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
+          <t>An taɓa yi wa yaron allurar kyanda?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
+          <t>4.10 Has this child ever received a measles vaccination?</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3507,7 +3503,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>${q4_08_card} = '2'</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -3528,17 +3528,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q4_12a_more_than_one</t>
+          <t>q4_11_diarrhoea</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>An sha fiye da magani ɗaya?</t>
+          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
+          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3548,11 +3548,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>${q4_12_antibiotic} = '1'</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -3568,32 +3564,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q4_13_placeholder_warning</t>
+          <t>q4_12_antibiotic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
+          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
+          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>${q4_12_antibiotic} = '1'</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -3609,22 +3605,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>select_one_from_file medicines.csv</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q4_13_medicine</t>
+          <t>q4_12a_more_than_one</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wane magani aka sha?</t>
+          <t>An sha fiye da magani ɗaya?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.13 Which antibiotic was taken?</t>
+          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3644,11 +3640,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
@@ -3658,34 +3650,30 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>q4_14_medicine_other</t>
+          <t>q4_13_placeholder_warning</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
+          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.14 Write the name of the medicine as reported</t>
+          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>${q4_13_medicine} = 'OTHER96'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3703,22 +3691,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one_from_file medicines.csv</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q4_15_no_prescription</t>
+          <t>q4_13_medicine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>An sami maganin ba tare da takardar likita ba?</t>
+          <t>Wane magani aka sha?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
+          <t>4.13 Which antibiotic was taken?</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3738,7 +3726,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
@@ -3748,22 +3740,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>select_one photo_taken</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q4_16_photo_status</t>
+          <t>q4_14_medicine_other</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>An ɗauki hoton kunshin maganin?</t>
+          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4.16 Was a photograph of the medicine packaging taken?</t>
+          <t>4.14 Write the name of the medicine as reported</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3775,7 +3767,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>${q4_12_antibiotic} = '1'</t>
+          <t>${q4_13_medicine} = 'OTHER96'</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3793,22 +3785,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q4_16_photo</t>
+          <t>q4_15_no_prescription</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ɗauki hoton kunshin maganin</t>
+          <t>An sami maganin ba tare da takardar likita ba?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.16 Photograph of the medicine packaging</t>
+          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3820,7 +3812,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>${q4_16_photo_status} = '1'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3829,11 +3821,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>max-pixels=1024</t>
-        </is>
-      </c>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -3842,28 +3830,36 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one photo_taken</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>s5_specimen</t>
+          <t>q4_16_photo_status</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sashe 5: Tattara samfuri</t>
+          <t>An ɗauki hoton kunshin maganin?</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Section 5: Specimen collection</t>
+          <t>4.16 Was a photograph of the medicine packaging taken?</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>${q4_12_antibiotic} = '1'</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -3879,31 +3875,47 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q5_01_specimen_eligible</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+          <t>q4_16_photo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ɗauki hoton kunshin maganin</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4.16 Photograph of the medicine packaging</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>${q4_16_photo_status} = '1'</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
-        </is>
-      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>max-pixels=1024</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -3912,32 +3924,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>q5_01_note</t>
+          <t>s5_specimen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
+          <t>Sashe 5: Tattara samfuri</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
+          <t>Section 5: Specimen collection</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>${q5_01_specimen_eligible} = 0</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -3953,40 +3961,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>q5_02_specimen_obtained</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>An sami samfurin bayan gida daga yaron?</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>5.02 Was a stool specimen obtained from this child?</t>
-        </is>
-      </c>
+          <t>q5_01_specimen_eligible</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>${q5_01_specimen_eligible} = 1</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -3998,58 +3994,38 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>q5_03_label_serial</t>
+          <t>q5_01_note</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lambar lakabin samfuri (lamba 6)</t>
+          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
+          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end)</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Lambar ba ta cikin kewayon ƙungiyar ka ba. Duba lakabin.</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Serial is not within the range allocated to your team. Check the label.</t>
-        </is>
-      </c>
+          <t>${q5_01_specimen_eligible} = 0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>numbers</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
@@ -4059,28 +4035,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>check_digit_expected</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+          <t>q5_02_specimen_obtained</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>An sami samfurin bayan gida daga yaron?</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>5.02 Was a stool specimen obtained from this child?</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>${q5_01_specimen_eligible} = 1</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
-        </is>
-      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -4097,17 +4085,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>q5_03_check_digit</t>
+          <t>q5_03_label_serial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lambar tantancewa (bayan layin)</t>
+          <t>Lambar lakabin samfuri (lamba 6)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5.03 Check character (after the hyphen)</t>
+          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4124,22 +4112,26 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
+          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
+          <t>Lambar ba ta cikin kewayon ƙungiyar ka ba. Duba lakabin.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
+          <t>Serial is not within the range allocated to your team. Check the label.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>numbers</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
@@ -4154,7 +4146,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>specimen_label_full</t>
+          <t>check_digit_expected</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -4168,7 +4160,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
+          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -4182,22 +4174,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>q5_04_coldbox_time</t>
+          <t>q5_03_check_digit</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
+          <t>Lambar tantancewa (bayan layin)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5.04 Time the specimen was placed in the cold box</t>
+          <t>5.03 Check character (after the hyphen)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4212,9 +4204,21 @@
           <t>${q5_02_specimen_obtained} = '1'</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
@@ -4227,52 +4231,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>q5_05_coldbox_temp</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Zafin akwatin sanyi (°C)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>5.05 Temperature shown on the cold box thermometer</t>
-        </is>
-      </c>
+          <t>specimen_label_full</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Temperature must be between -20.0 and 40.0 °C.</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -4284,30 +4264,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>q5_05_temp_warn</t>
+          <t>q5_04_coldbox_time</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
+          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
+          <t>5.04 Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
+          <t>${q5_02_specimen_obtained} = '1'</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4325,22 +4309,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_one no_specimen_reason</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q5_06_reason</t>
+          <t>q5_05_coldbox_temp</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dalilin da ya sa ba a sami samfuri ba</t>
+          <t>Zafin akwatin sanyi (°C)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5.06 Reason no specimen was obtained</t>
+          <t>5.05 Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4352,12 +4336,24 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '2'</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Temperature must be between -20.0 and 40.0 °C.</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -4370,34 +4366,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>q5_07_reason_other</t>
+          <t>q5_05_temp_warn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bayyana dalilin</t>
+          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5.07 Specify</t>
+          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>${q5_06_reason} = '96'</t>
+          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4415,20 +4407,36 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one no_specimen_reason</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>s5_end</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+          <t>q5_06_reason</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dalilin da ya sa ba a sami samfuri ba</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>5.06 Reason no specimen was obtained</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '2'</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4444,20 +4452,36 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>child_end</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+          <t>q5_07_reason_other</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bayyana dalilin</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>5.07 Specify</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>${q5_06_reason} = '96'</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4473,32 +4497,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>s6_environment</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Sashe 6: Yanayin gida</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Section 6: Household environment</t>
-        </is>
-      </c>
+          <t>s5_end</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4514,31 +4526,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one water_source</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>q6_01_water</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>6.01 What is the main source of drinking water for this household?</t>
-        </is>
-      </c>
+          <t>child_end</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -4555,32 +4555,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>q6_02_toilet</t>
+          <t>s6_environment</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
+          <t>Sashe 6: Yanayin gida</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6.02 What kind of toilet facility do members of this household use?</t>
+          <t>Section 6: Household environment</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -4596,22 +4596,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one water_source</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>q6_03_livestock</t>
+          <t>q6_01_water</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
+          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
+          <t>6.01 What is the main source of drinking water for this household?</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4637,22 +4637,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>q6_04_animal_antibiotic</t>
+          <t>q6_02_toilet</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
+          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.02 What kind of toilet facility do members of this household use?</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4662,11 +4662,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>${q6_03_livestock} = '1'</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4682,22 +4678,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one handwashing</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>q6_05_handwashing</t>
+          <t>q6_03_livestock</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
+          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
+          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4728,17 +4724,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>q6_06_hh_diarrhoea</t>
+          <t>q6_04_animal_antibiotic</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
+          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4748,7 +4744,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>${q6_03_livestock} = '1'</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4764,22 +4764,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_multiple assets</t>
+          <t>select_one handwashing</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>q6_07_assets</t>
+          <t>q6_05_handwashing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6.07 Which of the following does this household own?</t>
+          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4790,21 +4790,9 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be selected together with any other item.</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -4817,19 +4805,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>s6_end</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
+          <t>q6_06_hh_diarrhoea</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -4846,31 +4846,47 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_multiple assets</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>s7_closeout</t>
+          <t>q6_07_assets</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sashe 7: Kammalawa</t>
+          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Section 7: Close-out and supervisor review</t>
+          <t>6.07 Which of the following does this household own?</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be selected together with any other item.</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -4883,12 +4899,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>interview_duration_min</t>
+          <t>s6_end</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -4900,11 +4916,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
-        </is>
-      </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
@@ -4916,22 +4928,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>q7_02_observation</t>
+          <t>s7_closeout</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Duk wani abin lura da zai taimaka wa ofis</t>
+          <t>Sashe 7: Kammalawa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7.02 Record any observation that may help the office interpret this form</t>
+          <t>Section 7: Close-out and supervisor review</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4943,11 +4955,7 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
@@ -4957,24 +4965,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>select_one_from_file staff_roster.csv</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>q7_04_supervisor</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Lambar mai kula</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>7.04 Supervisor code</t>
-        </is>
-      </c>
+          <t>interview_duration_min</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -4982,17 +4982,13 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>role='Team supervisor'</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
@@ -5002,38 +4998,38 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>select_one supervisor_decision</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>q7_05_supervisor_decision</t>
+          <t>q7_02_observation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Shawarar mai kula kan wannan takarda</t>
+          <t>Duk wani abin lura da zai taimaka wa ofis</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7.05 Supervisor decision on this form</t>
+          <t>7.02 Record any observation that may help the office interpret this form</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>${q7_04_supervisor} != ''</t>
-        </is>
-      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
@@ -5043,16 +5039,24 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one_from_file staff_roster.csv</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>s7_end</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
+          <t>q7_04_supervisor</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Lambar mai kula</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>7.04 Supervisor code</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -5061,13 +5065,91 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>role='Team supervisor'</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>select_one supervisor_decision</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>q7_05_supervisor_decision</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Shawarar mai kula kan wannan takarda</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>7.05 Supervisor decision on this form</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>${q7_04_supervisor} != ''</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>s7_end</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -4112,17 +4112,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end)</t>
+          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end) and count(/data/child/s5_specimen[q5_03_label_serial = current()/.]) = 1 and count(${last-saved#q5_03_label_serial}[. = current()/.]) = 0</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lambar ba ta cikin kewayon ƙungiyar ka ba. Duba lakabin.</t>
+          <t>Lambar ba ta dace ba: ko ba ta cikin kewayon ƙungiyar ka ba, ko an riga an yi amfani da ita. Duba lakabin.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Serial is not within the range allocated to your team. Check the label.</t>
+          <t>Label rejected: it is either outside your team's allocated range, already used for another child in this household, or the label used in your previous submission. Check the label book.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:S114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,12 +605,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>deviceid</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>device_id</t>
+          <t>form_version</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -622,7 +622,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>'2026063001'</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -634,12 +638,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>deviceid</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>device_id</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -654,11 +658,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>track-changes=true identify-user=true track-changes-reasons=on-form-edit</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -667,24 +667,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>s0_login</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Shiga</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sign in</t>
-        </is>
-      </c>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -695,7 +687,11 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>track-changes=true identify-user=true track-changes-reasons=on-form-edit</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -704,42 +700,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_from_file staff_roster.csv</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>enumerator_code</t>
+          <t>s0_login</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lambar mai tambaya</t>
+          <t>Shiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enumerator code (1.08)</t>
+          <t>Sign in</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -749,30 +737,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one_from_file staff_roster.csv</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>enum_team</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>enumerator_code</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lambar mai tambaya</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enumerator code (1.08)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/team_code</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>enum_role</t>
+          <t>enum_team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -801,7 +801,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/role</t>
+          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/team_code</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>enum_lga</t>
+          <t>enum_role</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -834,7 +834,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/assigned_lga</t>
+          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/role</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>enum_pin</t>
+          <t>enum_lga</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -867,7 +867,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/pin</t>
+          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/assigned_lga</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -881,54 +881,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pin_entered</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Shigar da PIN dinka</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Enter your 4-digit PIN</t>
-        </is>
-      </c>
+          <t>enum_pin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string-length(.) = 4 and . = ${enum_pin}</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>PIN din bai dace ba. Sake gwadawa.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>PIN does not match this enumerator code.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/pin</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>numbers masked</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -938,22 +914,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_from_file specimen_label_allocation.csv</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>q0_label_range</t>
+          <t>pin_entered</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tabbatar da littafin lakabin ƙungiyar ka</t>
+          <t>Shigar da PIN dinka</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Confirm the specimen label book issued to your team</t>
+          <t>Enter your 4-digit PIN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -964,18 +940,26 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string-length(.) = 4 and . = ${enum_pin}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PIN din bai dace ba. Sake gwadawa.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PIN does not match this enumerator code.</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>team_code=${enum_team}</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>numbers masked</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -987,34 +971,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one_from_file specimen_label_allocation.csv</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>team_note</t>
+          <t>q0_label_range</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ƙungiya: ${enum_team}  |  LGA: ${enum_lga}</t>
+          <t>Tabbatar da littafin lakabin ƙungiyar ka</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Team: ${enum_team}  |  LGA: ${enum_lga}</t>
+          <t>Confirm the specimen label book issued to your team</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>team_code=${enum_team}</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1024,16 +1020,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>s0_login_end</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>team_note</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ƙungiya: ${enum_team}  |  LGA: ${enum_lga}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Team: ${enum_team}  |  LGA: ${enum_lga}</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1053,24 +1057,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>s1_identification</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sashe 1: Bayanin gida</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Section 1: Household identification</t>
-        </is>
-      </c>
+          <t>s0_login_end</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1090,16 +1086,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>q1_01_state</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>s1_identification</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sashe 1: Bayanin gida</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Section 1: Household identification</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1107,11 +1111,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>'BAN'</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1123,48 +1123,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_from_file lgas.csv</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>q1_02_lga</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Karamar hukuma</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.02 Local Government Area</t>
-        </is>
-      </c>
+          <t>q1_01_state</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>. = ${enum_lga} or ${enum_role} != 'Enumerator'</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Ba a ba ka wannan karamar hukuma ba.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>This LGA is not the one assigned to you. Check with your supervisor.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>'BAN'</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1176,22 +1156,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_from_file wards.csv</t>
+          <t>select_one_from_file lgas.csv</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>q1_03_ward</t>
+          <t>q1_02_lga</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gunduma</t>
+          <t>Karamar hukuma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.03 Ward</t>
+          <t>1.02 Local Government Area</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1202,20 +1182,24 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>. = ${enum_lga} or ${enum_role} != 'Enumerator'</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Ba a ba ka wannan karamar hukuma ba.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>This LGA is not the one assigned to you. Check with your supervisor.</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lga_code=${q1_02_lga}</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1225,22 +1209,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_from_file settlements.csv</t>
+          <t>select_one_from_file wards.csv</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>q1_04_settlement</t>
+          <t>q1_03_ward</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ƙauye / unguwa</t>
+          <t>Gunduma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.04 Settlement</t>
+          <t>1.03 Ward</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1257,7 +1241,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ward_code=${q1_03_ward}</t>
+          <t>lga_code=${q1_02_lga}</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1274,22 +1258,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one_from_file settlements.csv</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>q1_05_alt_name_yn</t>
+          <t>q1_04_settlement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ana kiran wannan wuri da wani suna daban?</t>
+          <t>Ƙauye / unguwa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.05 Is the settlement known locally by a different name?</t>
+          <t>1.04 Settlement</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1304,8 +1288,16 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ward_code=${q1_03_ward}</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -1315,22 +1307,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>q1_05_alt_name</t>
+          <t>q1_05_alt_name_yn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rubuta sunan da ake amfani da shi a nan</t>
+          <t>Ana kiran wannan wuri da wani suna daban?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.05 Local name</t>
+          <t>1.05 Is the settlement known locally by a different name?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1340,11 +1332,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>${q1_05_alt_name_yn} = '1'</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1360,22 +1348,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>q1_06_structure</t>
+          <t>q1_05_alt_name</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lambar gini da aka rubuta a gidan</t>
+          <t>Rubuta sunan da ake amfani da shi a nan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.06 Structure number painted on the dwelling</t>
+          <t>1.05 Local name</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1385,22 +1373,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 999</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Lamba tsakanin 1 zuwa 999.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Enter a number between 1 and 999.</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>${q1_05_alt_name_yn} = '1'</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -1418,17 +1398,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>q1_07_hh_serial</t>
+          <t>q1_06_structure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lambar gida a cikin ƙauyen</t>
+          <t>Lambar gini da aka rubuta a gidan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.07 Household serial number within the settlement</t>
+          <t>1.06 Structure number painted on the dwelling</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1466,22 +1446,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>q1_10_visit_date</t>
+          <t>q1_07_hh_serial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ranar ziyara</t>
+          <t>Lambar gida a cikin ƙauyen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.10 Date of visit</t>
+          <t>1.07 Household serial number within the settlement</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1494,17 +1474,17 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>. &gt;= date('2026-06-01') and . &lt;= date('2026-06-30')</t>
+          <t>. &gt;= 1 and . &lt;= 999</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ranar dole ta kasance tsakanin 1 zuwa 30 ga Yuni 2026.</t>
+          <t>Lamba tsakanin 1 zuwa 999.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Date must fall within the fieldwork window, 1-30 June 2026.</t>
+          <t>Enter a number between 1 and 999.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1513,32 +1493,28 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>today()</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>q1_11_gps</t>
+          <t>q1_10_visit_date</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ɗauki wurin GPS a ƙofar gidan</t>
+          <t>Ranar ziyara</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.11 GPS reading at the entrance to the dwelling</t>
+          <t>1.10 Date of visit</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1549,37 +1525,53 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>. &gt;= date('2026-06-01') and . &lt;= date('2026-06-30')</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ranar dole ta kasance tsakanin 1 zuwa 30 ga Yuni 2026.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Date must fall within the fieldwork window, 1-30 June 2026.</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>today()</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>q1_12_prev_round</t>
+          <t>q1_11_gps</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>An ziyarci wannan gida a watan Oktoba 2025?</t>
+          <t>Ɗauki wurin GPS a ƙofar gidan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.12 Was this household visited during the October 2025 round?</t>
+          <t>1.11 GPS reading at the entrance to the dwelling</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1605,22 +1597,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one_from_file previous_round_households.csv</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>q1_13_prev_id</t>
+          <t>q1_12_prev_round</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lambar gidan da aka ba shi a 2025</t>
+          <t>An ziyarci wannan gida a watan Oktoba 2025?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.13 Household identifier allocated in the October 2025 round</t>
+          <t>1.12 Was this household visited during the October 2025 round?</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1630,25 +1622,13 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>${q1_12_prev_round} = '1'</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>settlement_id=${q1_04_settlement}</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -1658,22 +1638,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one result_of_visit</t>
+          <t>select_one_from_file previous_round_households.csv</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>q1_14_result</t>
+          <t>q1_13_prev_id</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sakamakon ziyarar</t>
+          <t>Lambar gidan da aka ba shi a 2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.14 Result of visit</t>
+          <t>1.13 Household identifier allocated in the October 2025 round</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1683,13 +1663,25 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>${q1_12_prev_round} = '1'</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>settlement_id=${q1_04_settlement}</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -1699,32 +1691,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one result_of_visit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>q1_14_stop_note</t>
+          <t>q1_14_result</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kada ka ci gaba. Sa hannu a 7.03 sannan ka mika wa mai kula da kai.</t>
+          <t>Sakamakon ziyarar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Do not complete any further section. Sign at 7.03 and hand the form to your supervisor.</t>
+          <t>1.14 Result of visit</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>${q1_14_result} != '1'</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1740,20 +1732,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>s1_end</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>q1_14_stop_note</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kada ka ci gaba. Sa hannu a 7.03 sannan ka mika wa mai kula da kai.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Do not complete any further section. Sign at 7.03 and hand the form to your supervisor.</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>${q1_14_result} != '1'</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1769,32 +1773,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>s2_consent</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sashe 2: Yarda</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Section 2: Consent</t>
-        </is>
-      </c>
+          <t>s1_end</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1'</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -1810,47 +1802,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>q2_01_statement_read</t>
+          <t>s2_consent</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>An karanta sanarwar yarda gaba ɗaya ga mai amsa?</t>
+          <t>Sashe 2: Yarda</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.01 Consent statement read aloud to the respondent in full?</t>
+          <t>Section 2: Consent</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>. = '1'</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Dole ne a karanta sanarwar yarda gaba ɗaya kafin a ci gaba.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>The consent statement must be read in full before continuing. Read it now, then record Yes.</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1'</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -1863,22 +1843,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one consent</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>q2_02_consent</t>
+          <t>q2_01_statement_read</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mai amsa ya yarda da tambayoyin?</t>
+          <t>An karanta sanarwar yarda gaba ɗaya ga mai amsa?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.02 Does the respondent consent to the household interview?</t>
+          <t>2.01 Consent statement read aloud to the respondent in full?</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1889,9 +1869,21 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>. = '1'</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Dole ne a karanta sanarwar yarda gaba ɗaya kafin a ci gaba.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>The consent statement must be read in full before continuing. Read it now, then record Yes.</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -1904,22 +1896,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_one relationship</t>
+          <t>select_one consent</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>q2_03_relationship</t>
+          <t>q2_02_consent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alaƙar mai amsa da shugaban gida</t>
+          <t>Mai amsa ya yarda da tambayoyin?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.03 Relationship of the respondent to the head of household</t>
+          <t>2.02 Does the respondent consent to the household interview?</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1929,11 +1921,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1949,20 +1937,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one relationship</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>s2_end</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+          <t>q2_03_relationship</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Alaƙar mai amsa da shugaban gida</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.03 Relationship of the respondent to the head of household</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -1978,32 +1982,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>s3_roster</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Sashe 3: Jerin mazauna gida</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Section 3: Household roster</t>
-        </is>
-      </c>
+          <t>s2_end</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2019,47 +2011,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>q3_01_hh_size</t>
+          <t>s3_roster</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mutane nawa ne ke zama a wannan gida?</t>
+          <t>Sashe 3: Jerin mazauna gida</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.01 How many people usually live in this household?</t>
+          <t>Section 3: Household roster</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 40</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Adadi tsakanin 1 zuwa 40. Idan ya fi haka, sanar da mai kula da kai.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Enter between 1 and 40. If larger, notify your supervisor.</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -2072,40 +2052,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>roster</t>
+          <t>q3_01_hh_size</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mazaunin gida</t>
+          <t>Mutane nawa ne ke zama a wannan gida?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Resident</t>
+          <t>3.01 How many people usually live in this household?</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 40</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Adadi tsakanin 1 zuwa 40. Idan ya fi haka, sanar da mai kula da kai.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Enter between 1 and 40. If larger, notify your supervisor.</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>${q3_01_hh_size}</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2113,16 +2105,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>line_no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>roster</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mazaunin gida</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Resident</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -2130,15 +2130,15 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>position(..)</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>${q3_01_hh_size}</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2146,24 +2146,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>line_note</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Layi ${line_no}</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Line ${line_no}</t>
-        </is>
-      </c>
+          <t>line_no</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -2171,7 +2163,11 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>position(..)</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2183,39 +2179,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>r_initials</t>
+          <t>line_note</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baƙaƙen farko na suna</t>
+          <t>Layi ${line_no}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(2) Initials</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Baƙaƙen farko kawai, ba cikakken suna ba.</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Initials only - do not record the full name.</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Line ${line_no}</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -2232,26 +2216,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one relationship</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>r_relationship</t>
+          <t>r_initials</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alaƙa da shugaban gida</t>
+          <t>Baƙaƙen farko na suna</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(3) Relationship to head</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+          <t>(2) Initials</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Baƙaƙen farko kawai, ba cikakken suna ba.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Initials only - do not record the full name.</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2273,22 +2265,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>select_one relationship</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>r_sex</t>
+          <t>r_relationship</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jinsi</t>
+          <t>Alaƙa da shugaban gida</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(4) Sex</t>
+          <t>(3) Relationship to head</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2314,34 +2306,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>select_one age_unit</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>r_age_unit</t>
+          <t>r_sex</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shekaru ko watanni?</t>
+          <t>Jinsi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Age recorded in years or months?</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Watanni ga yara ƙasa da shekara 5.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Months for children under 5 years.</t>
-        </is>
-      </c>
+          <t>(4) Sex</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2363,51 +2347,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one age_unit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>r_age_years</t>
+          <t>r_age_unit</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shekaru cikakku</t>
+          <t>Shekaru ko watanni?</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(5) Age in completed years</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+          <t>Age recorded in years or months?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Watanni ga yara ƙasa da shekara 5.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Months for children under 5 years.</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>${r_age_unit} = 'years'</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>. &gt;= 5 and . &lt;= 120</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Shekaru 5 zuwa 120. Ga yara ƙasa da 5, yi amfani da watanni.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>5 to 120 years. For children under 5, record months instead.</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -2425,17 +2401,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>r_age_months</t>
+          <t>r_age_years</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Watanni cikakku</t>
+          <t>Shekaru cikakku</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(6) Age in completed months</t>
+          <t>(5) Age in completed years</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2447,22 +2423,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>${r_age_unit} = 'months'</t>
+          <t>${r_age_unit} = 'years'</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 59</t>
+          <t>. &gt;= 5 and . &lt;= 120</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Watanni 0 zuwa 59. Idan ya kai watanni 60, yi amfani da shekaru.</t>
+          <t>Shekaru 5 zuwa 120. Ga yara ƙasa da 5, yi amfani da watanni.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0 to 59 months. At 60 months and above, record age in years.</t>
+          <t>5 to 120 years. For children under 5, record months instead.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -2477,28 +2453,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>r_eligible</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>r_age_months</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Watanni cikakku</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>(6) Age in completed months</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>if(${r_age_unit} = 'months' and ${r_age_months} &gt;= 9 and ${r_age_months} &lt;= 59, 1, 0)</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>${r_age_unit} = 'months'</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 59</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Watanni 0 zuwa 59. Idan ya kai watanni 60, yi amfani da shekaru.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0 to 59 months. At 60 months and above, record age in years.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -2510,12 +2510,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>roster_end</t>
+          <t>r_eligible</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2527,7 +2527,11 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>if(${r_age_unit} = 'months' and ${r_age_months} &gt;= 9 and ${r_age_months} &lt;= 59, 1, 0)</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -2539,12 +2543,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>roster_count</t>
+          <t>roster_end</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -2556,11 +2560,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>count(${roster})</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>q3_02_eligible</t>
+          <t>roster_count</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>sum(${r_eligible})</t>
+          <t>count(${roster})</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -2605,36 +2605,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>roster_mismatch_note</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>⚠ Ka ce mutane ${q3_01_hh_size} ne, amma ka rubuta ${roster_count}. Duba kafin ka ci gaba.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>⚠ You recorded ${q3_01_hh_size} usual residents but listed ${roster_count}. Check the roster before continuing.</t>
-        </is>
-      </c>
+          <t>q3_02_eligible</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>${roster_count} != ${q3_01_hh_size}</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>sum(${r_eligible})</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -2651,23 +2643,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>q3_02_note</t>
+          <t>roster_mismatch_note</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yara masu watanni 9-59 a wannan gida: ${q3_02_eligible}</t>
+          <t>⚠ Ka ce mutane ${q3_01_hh_size} ne, amma ka rubuta ${roster_count}. Duba kafin ka ci gaba.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.02 Children aged 9-59 completed months in this household: ${q3_02_eligible}</t>
+          <t>⚠ You recorded ${q3_01_hh_size} usual residents but listed ${roster_count}. Check the roster before continuing.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>${roster_count} != ${q3_01_hh_size}</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -2683,16 +2679,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>s3_end</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+          <t>q3_02_note</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Yara masu watanni 9-59 a wannan gida: ${q3_02_eligible}</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.02 Children aged 9-59 completed months in this household: ${q3_02_eligible}</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -2712,32 +2716,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Yaro</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Child</t>
-        </is>
-      </c>
+          <t>s3_end</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1' and ${q3_02_eligible} &gt; 0</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2745,11 +2737,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>${q3_02_eligible}</t>
-        </is>
-      </c>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -2757,32 +2745,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>child_index</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yaro</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1' and ${q3_02_eligible} &gt; 0</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>position(..)</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>${q3_02_eligible}</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -2790,48 +2790,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>q4_01_line</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Layin yaron a jerin mazauna</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>4.01 Line number of this child in the Section 3 roster</t>
-        </is>
-      </c>
+          <t>child_index</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>position(..)</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -2843,28 +2823,48 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>q4_02_initials</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>q4_01_line</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Layin yaron a jerin mazauna</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4.01 Line number of this child in the Section 3 roster</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>indexed-repeat(${r_initials}, ${roster}, ${q4_01_line})</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>q4_03_age_months</t>
+          <t>q4_02_initials</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>indexed-repeat(${r_age_months}, ${roster}, ${q4_01_line})</t>
+          <t>indexed-repeat(${r_initials}, ${roster}, ${q4_01_line})</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -2909,24 +2909,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>child_age_note</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Watanni: ${q4_03_age_months}</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>4.03 Age in completed months (from roster): ${q4_03_age_months}</t>
-        </is>
-      </c>
+          <t>q4_03_age_months</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
@@ -2934,7 +2926,11 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>indexed-repeat(${r_age_months}, ${roster}, ${q4_01_line})</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -2946,31 +2942,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>q4_04_sex</t>
+          <t>child_age_note</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jinsin yaron</t>
+          <t>Watanni: ${q4_03_age_months}</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.04 Sex of the child</t>
+          <t>4.03 Age in completed months (from roster): ${q4_03_age_months}</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -2987,22 +2979,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one measured</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>q4_05_weight_status</t>
+          <t>q4_04_sex</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>An auna nauyin yaron?</t>
+          <t>Jinsin yaron</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.05 Was the child weighed?</t>
+          <t>4.04 Sex of the child</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3028,22 +3020,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one measured</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>q4_05_weight_kg</t>
+          <t>q4_05_weight_status</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nauyi (kg)</t>
+          <t>An auna nauyin yaron?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4.05 Weight in kg</t>
+          <t>4.05 Was the child weighed?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3053,26 +3045,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>${q4_05_weight_status} = 'measured'</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>. &gt;= 2.0 and . &lt;= 30.0</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Nauyi tsakanin 2.0 zuwa 30.0 kg.</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Weight must be between 2.0 and 30.0 kg for a child aged 9-59 months.</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -3085,35 +3061,51 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>weight_implausible_warn</t>
+          <t>q4_05_weight_kg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>⚠ Wannan nauyin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
+          <t>Nauyi (kg)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>⚠ This weight is outside the usual range for a child aged ${q4_03_age_months} months. Re-weigh to confirm, then record what you measure.</t>
+          <t>4.05 Weight in kg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>${q4_05_weight_status} = 'measured' and (${q4_05_weight_kg} &lt; 5.0 or ${q4_05_weight_kg} &gt; 28.0)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>${q4_05_weight_status} = 'measured'</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>. &gt;= 2.0 and . &lt;= 30.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Nauyi tsakanin 2.0 zuwa 30.0 kg.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Weight must be between 2.0 and 30.0 kg for a child aged 9-59 months.</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -3126,32 +3118,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>select_one measured</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>q4_06_height_status</t>
+          <t>weight_implausible_warn</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>An auna tsayin yaron?</t>
+          <t>⚠ Wannan nauyin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.06 Was the child measured?</t>
+          <t>⚠ This weight is outside the usual range for a child aged ${q4_03_age_months} months. Re-weigh to confirm, then record what you measure.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>${q4_05_weight_status} = 'measured' and (${q4_05_weight_kg} &lt; 5.0 or ${q4_05_weight_kg} &gt; 28.0)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3167,22 +3159,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one measured</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>q4_06_height_cm</t>
+          <t>q4_06_height_status</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tsayi (cm)</t>
+          <t>An auna tsayin yaron?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.06 Length or height in cm</t>
+          <t>4.06 Was the child measured?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3192,26 +3184,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>${q4_06_height_status} = 'measured'</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3224,35 +3200,51 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>height_implausible_warn</t>
+          <t>q4_06_height_cm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>⚠ Wannan tsayin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
+          <t>Tsayi (cm)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>⚠ This height is outside the usual range for a child aged ${q4_03_age_months} months. Re-measure to confirm, then record what you measure.</t>
+          <t>4.06 Length or height in cm</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>${q4_06_height_status} = 'measured' and (${q4_06_height_cm} &lt; 60.0 or ${q4_06_height_cm} &gt; 125.0)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+          <t>${q4_06_height_status} = 'measured'</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -3265,34 +3257,30 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>select_one measure_position</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>q4_07_position</t>
+          <t>height_implausible_warn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yadda aka auna yaron</t>
+          <t>⚠ Wannan tsayin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.07 Position in which the child was measured</t>
+          <t>⚠ This height is outside the usual range for a child aged ${q4_03_age_months} months. Re-measure to confirm, then record what you measure.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>${q4_06_height_status} = 'measured'</t>
+          <t>${q4_06_height_status} = 'measured' and (${q4_06_height_cm} &lt; 60.0 or ${q4_06_height_cm} &gt; 125.0)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3310,30 +3298,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one measure_position</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q4_07_position_warn</t>
+          <t>q4_07_position</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
+          <t>Yadda aka auna yaron</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
+          <t>4.07 Position in which the child was measured</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
+          <t>${q4_06_height_status} = 'measured'</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3351,32 +3343,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>select_one card_seen</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q4_08_card</t>
+          <t>q4_07_position_warn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Za a iya ganin katin rigakafi na yaron?</t>
+          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.08 May I see the child's vaccination card or health record?</t>
+          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3392,32 +3384,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>select_one document_type</t>
+          <t>select_one card_seen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>q4_08a_doc_type</t>
+          <t>q4_08_card</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wane irin takarda aka gani?</t>
+          <t>Za a iya ganin katin rigakafi na yaron?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
+          <t>4.08 May I see the child's vaccination card or health record?</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>${q4_08_card} = '1'</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3433,31 +3425,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one document_type</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q4_09_measles_card</t>
+          <t>q4_08a_doc_type</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>An rubuta allurar kyanda a katin?</t>
+          <t>Wane irin takarda aka gani?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4.09 Copy from the card: is a measles dose recorded?</t>
+          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>${q4_08_card} = '1'</t>
@@ -3478,22 +3466,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q4_10_measles_recall</t>
+          <t>q4_09_measles_card</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>An taɓa yi wa yaron allurar kyanda?</t>
+          <t>An rubuta allurar kyanda a katin?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.10 Has this child ever received a measles vaccination?</t>
+          <t>4.09 Copy from the card: is a measles dose recorded?</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3505,7 +3493,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>${q4_08_card} = '2'</t>
+          <t>${q4_08_card} = '1'</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3528,17 +3516,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q4_11_diarrhoea</t>
+          <t>q4_10_measles_recall</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
+          <t>An taɓa yi wa yaron allurar kyanda?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
+          <t>4.10 Has this child ever received a measles vaccination?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3548,7 +3536,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>${q4_08_card} = '2'</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -3569,17 +3561,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q4_12_antibiotic</t>
+          <t>q4_11_diarrhoea</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
+          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
+          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3610,17 +3602,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q4_12a_more_than_one</t>
+          <t>q4_12_antibiotic</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>An sha fiye da magani ɗaya?</t>
+          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
+          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3630,11 +3622,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>${q4_12_antibiotic} = '1'</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -3650,27 +3638,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>q4_13_placeholder_warning</t>
+          <t>q4_12a_more_than_one</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
+          <t>An sha fiye da magani ɗaya?</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
+          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>${q4_12_antibiotic} = '1'</t>
@@ -3691,31 +3683,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one_from_file medicines.csv</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q4_13_medicine</t>
+          <t>q4_13_placeholder_warning</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wane magani aka sha?</t>
+          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4.13 Which antibiotic was taken?</t>
+          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>${q4_12_antibiotic} = '1'</t>
@@ -3726,11 +3714,7 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
@@ -3740,22 +3724,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file medicines.csv</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q4_14_medicine_other</t>
+          <t>q4_13_medicine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
+          <t>Wane magani aka sha?</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4.14 Write the name of the medicine as reported</t>
+          <t>4.13 Which antibiotic was taken?</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3767,7 +3751,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>${q4_13_medicine} = 'OTHER96'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3775,7 +3759,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
@@ -3785,22 +3773,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q4_15_no_prescription</t>
+          <t>q4_14_medicine_other</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>An sami maganin ba tare da takardar likita ba?</t>
+          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
+          <t>4.14 Write the name of the medicine as reported</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3812,7 +3800,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>${q4_12_antibiotic} = '1'</t>
+          <t>${q4_13_medicine} = 'OTHER96'</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3830,22 +3818,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>select_one photo_taken</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>q4_16_photo_status</t>
+          <t>q4_15_no_prescription</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>An ɗauki hoton kunshin maganin?</t>
+          <t>An sami maganin ba tare da takardar likita ba?</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4.16 Was a photograph of the medicine packaging taken?</t>
+          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3875,22 +3863,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one photo_taken</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q4_16_photo</t>
+          <t>q4_16_photo_status</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ɗauki hoton kunshin maganin</t>
+          <t>An ɗauki hoton kunshin maganin?</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4.16 Photograph of the medicine packaging</t>
+          <t>4.16 Was a photograph of the medicine packaging taken?</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3902,7 +3890,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>${q4_16_photo_status} = '1'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3911,11 +3899,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>max-pixels=1024</t>
-        </is>
-      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -3924,35 +3908,47 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>s5_specimen</t>
+          <t>q4_16_photo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sashe 5: Tattara samfuri</t>
+          <t>Ɗauki hoton kunshin maganin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Section 5: Specimen collection</t>
+          <t>4.16 Photograph of the medicine packaging</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>${q4_16_photo_status} = '1'</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>max-pixels=1024</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -3961,16 +3957,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>q5_01_specimen_eligible</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+          <t>s5_specimen</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sashe 5: Tattara samfuri</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Section 5: Specimen collection</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
@@ -3978,11 +3982,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
-        </is>
-      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -3994,36 +3994,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>q5_01_note</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
-        </is>
-      </c>
+          <t>q5_01_specimen_eligible</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>${q5_01_specimen_eligible} = 0</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -4035,34 +4027,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>q5_02_specimen_obtained</t>
+          <t>q5_01_note</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>An sami samfurin bayan gida daga yaron?</t>
+          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5.02 Was a stool specimen obtained from this child?</t>
+          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>${q5_01_specimen_eligible} = 1</t>
+          <t>${q5_01_specimen_eligible} = 0</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -4080,22 +4068,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>q5_03_label_serial</t>
+          <t>q5_02_specimen_obtained</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lambar lakabin samfuri (lamba 6)</t>
+          <t>An sami samfurin bayan gida daga yaron?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
+          <t>5.02 Was a stool specimen obtained from this child?</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4107,31 +4095,15 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end) and count(/data/child/s5_specimen[q5_03_label_serial = current()/.]) = 1 and count(${last-saved#q5_03_label_serial}[. = current()/.]) = 0</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Lambar ba ta dace ba: ko ba ta cikin kewayon ƙungiyar ka ba, ko an riga an yi amfani da ita. Duba lakabin.</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Label rejected: it is either outside your team's allocated range, already used for another child in this household, or the label used in your previous submission. Check the label book.</t>
-        </is>
-      </c>
+          <t>${q5_01_specimen_eligible} = 1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>numbers</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
@@ -4141,30 +4113,58 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>check_digit_expected</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+          <t>q5_03_label_serial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Lambar lakabin samfuri (lamba 6)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end) and count(/data/child/s5_specimen[q5_03_label_serial = current()/.]) = 1 and count(${last-saved#q5_03_label_serial}[. = current()/.]) = 0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Lambar ba ta dace ba: ko ba ta cikin kewayon ƙungiyar ka ba, ko an riga an yi amfani da ita. Duba lakabin.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Label rejected: it is either outside your team's allocated range, already used for another child in this household, or the label used in your previous submission. Check the label book.</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>numbers</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
@@ -4174,52 +4174,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>q5_03_check_digit</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Lambar tantancewa (bayan layin)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>5.03 Check character (after the hyphen)</t>
-        </is>
-      </c>
+          <t>check_digit_expected</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
@@ -4231,28 +4207,52 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>specimen_label_full</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+          <t>q5_03_check_digit</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Lambar tantancewa (bayan layin)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5.03 Check character (after the hyphen)</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -4264,40 +4264,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>q5_04_coldbox_time</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>5.04 Time the specimen was placed in the cold box</t>
-        </is>
-      </c>
+          <t>specimen_label_full</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
@@ -4309,22 +4297,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q5_05_coldbox_temp</t>
+          <t>q5_04_coldbox_time</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Zafin akwatin sanyi (°C)</t>
+          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5.05 Temperature shown on the cold box thermometer</t>
+          <t>5.04 Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4339,21 +4327,9 @@
           <t>${q5_02_specimen_obtained} = '1'</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Temperature must be between -20.0 and 40.0 °C.</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -4366,35 +4342,51 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>q5_05_temp_warn</t>
+          <t>q5_05_coldbox_temp</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
+          <t>Zafin akwatin sanyi (°C)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
+          <t>5.05 Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Temperature must be between -20.0 and 40.0 °C.</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
@@ -4407,34 +4399,30 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_one no_specimen_reason</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>q5_06_reason</t>
+          <t>q5_05_temp_warn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dalilin da ya sa ba a sami samfuri ba</t>
+          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5.06 Reason no specimen was obtained</t>
+          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '2'</t>
+          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4452,22 +4440,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one no_specimen_reason</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>q5_07_reason_other</t>
+          <t>q5_06_reason</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bayyana dalilin</t>
+          <t>Dalilin da ya sa ba a sami samfuri ba</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5.07 Specify</t>
+          <t>5.06 Reason no specimen was obtained</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4479,7 +4467,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>${q5_06_reason} = '96'</t>
+          <t>${q5_02_specimen_obtained} = '2'</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4497,20 +4485,36 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>s5_end</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+          <t>q5_07_reason_other</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bayyana dalilin</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>5.07 Specify</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>${q5_06_reason} = '96'</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4526,12 +4530,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>child_end</t>
+          <t>s5_end</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -4555,32 +4559,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>s6_environment</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Sashe 6: Yanayin gida</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Section 6: Household environment</t>
-        </is>
-      </c>
+          <t>child_end</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -4596,32 +4588,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>select_one water_source</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>q6_01_water</t>
+          <t>s6_environment</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
+          <t>Sashe 6: Yanayin gida</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6.01 What is the main source of drinking water for this household?</t>
+          <t>Section 6: Household environment</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4637,22 +4629,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>select_one water_source</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>q6_02_toilet</t>
+          <t>q6_01_water</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
+          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.02 What kind of toilet facility do members of this household use?</t>
+          <t>6.01 What is the main source of drinking water for this household?</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4678,22 +4670,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>q6_03_livestock</t>
+          <t>q6_02_toilet</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
+          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
+          <t>6.02 What kind of toilet facility do members of this household use?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4719,22 +4711,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>q6_04_animal_antibiotic</t>
+          <t>q6_03_livestock</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
+          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4744,11 +4736,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>${q6_03_livestock} = '1'</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4764,22 +4752,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_one handwashing</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>q6_05_handwashing</t>
+          <t>q6_04_animal_antibiotic</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
+          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
+          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4789,7 +4777,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>${q6_03_livestock} = '1'</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -4805,22 +4797,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one handwashing</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>q6_06_hh_diarrhoea</t>
+          <t>q6_05_handwashing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
+          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4846,22 +4838,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>select_multiple assets</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>q6_07_assets</t>
+          <t>q6_06_hh_diarrhoea</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6.07 Which of the following does this household own?</t>
+          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4872,21 +4864,9 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be selected together with any other item.</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -4899,23 +4879,47 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_multiple assets</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>s6_end</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
+          <t>q6_07_assets</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>6.07 Which of the following does this household own?</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be selected together with any other item.</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
@@ -4928,24 +4932,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>s7_closeout</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Sashe 7: Kammalawa</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Section 7: Close-out and supervisor review</t>
-        </is>
-      </c>
+          <t>s6_end</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
@@ -4965,16 +4961,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>interview_duration_min</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+          <t>s7_closeout</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sashe 7: Kammalawa</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Section 7: Close-out and supervisor review</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -4982,11 +4986,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
-        </is>
-      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
@@ -4998,24 +4998,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>q7_02_observation</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Duk wani abin lura da zai taimaka wa ofis</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>7.02 Record any observation that may help the office interpret this form</t>
-        </is>
-      </c>
+          <t>interview_duration_min</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
@@ -5023,13 +5015,13 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
@@ -5039,22 +5031,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>select_one_from_file staff_roster.csv</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>q7_04_supervisor</t>
+          <t>q7_02_observation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lambar mai kula</t>
+          <t>Duk wani abin lura da zai taimaka wa ofis</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7.04 Supervisor code</t>
+          <t>7.02 Record any observation that may help the office interpret this form</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -5065,14 +5057,10 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>role='Team supervisor'</t>
-        </is>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>autocomplete</t>
+          <t>multiline</t>
         </is>
       </c>
       <c r="O111" t="inlineStr"/>
@@ -5084,38 +5072,42 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>select_one supervisor_decision</t>
+          <t>select_one_from_file staff_roster.csv</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>q7_05_supervisor_decision</t>
+          <t>q7_04_supervisor</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Shawarar mai kula kan wannan takarda</t>
+          <t>Lambar mai kula</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7.05 Supervisor decision on this form</t>
+          <t>7.04 Supervisor code</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>${q7_04_supervisor} != ''</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>role='Team supervisor'</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
@@ -5125,20 +5117,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one supervisor_decision</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>s7_end</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+          <t>q7_05_supervisor_decision</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Shawarar mai kula kan wannan takarda</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>7.05 Supervisor decision on this form</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>${q7_04_supervisor} != ''</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -5150,6 +5154,35 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>s7_end</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER_REPLACE_WITH_REAL_BASE64_PUBLIC_KEY</t>
+          <t>MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEAwgyOOePD+sEtA+ChZsUL1rsP8thmSPgfLaqu/dVxUplmX1dJn3hMTplFhAXqoNHz+ZufPTUsrflglTxoy8RczSGJqJ/nKzNX2QV6sIU6orJhPwoBNi7EWZiMflu0zw2yHVIwZbnpIxoMmOsWZkLSKnayn5sgALBes3PafOa7XdLypiaRYWdaBpnSewpvqy59aG/Tm3XtTB0t4UUUPjRStLwA/sABZWbSovS9pkQ8m7MCQFFhKs0KyZxpDb5HnwId1gU48hQkUsxyHMPUcZ7Xs0TuXBzlKz3xTt8mv4wOP5yuuVk2fXSwfhpF9Imj1dtl6ChsngaPGT3Qle42JZfmwwIDAQAB</t>
         </is>
       </c>
     </row>

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -867,7 +867,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/assigned_lga</t>
+          <t>instance('staff_roster')/root/item[name=${enumerator_code}]/assigned_lga_code</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S114"/>
+  <dimension ref="A1:S117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,7 +624,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>'2026063001'</t>
+          <t>'20260630-9c5d68'</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1638,50 +1638,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one_from_file previous_round_households.csv</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>q1_13_prev_id</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Lambar gidan da aka ba shi a 2025</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1.13 Household identifier allocated in the October 2025 round</t>
-        </is>
-      </c>
+          <t>q1_13_prev_n</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>${q1_12_prev_round} = '1'</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>settlement_id=${q1_04_settlement}</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>count(instance('previous_round_households')/root/item[settlement_id=${q1_04_settlement}])</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -1691,38 +1671,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one result_of_visit</t>
+          <t>select_one_from_file previous_round_households.csv</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>q1_14_result</t>
+          <t>q1_13_prev_id</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sakamakon ziyarar</t>
+          <t>Lambar gidan da aka ba shi a 2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.14 Result of visit</t>
+          <t>1.13 Household identifier allocated in the October 2025 round</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>${q1_12_prev_round} = '1' and ${q1_13_prev_n} &gt; 0</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>settlement_id=${q1_04_settlement}</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -1732,35 +1724,51 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>q1_14_stop_note</t>
+          <t>q1_13_prev_id_other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kada ka ci gaba. Sa hannu a 7.03 sannan ka mika wa mai kula da kai.</t>
+          <t>Rubuta lambar gidan ta 2025 kamar yadda take a katin gidan (misali BAN-000123). Idan ba a sani ba, rubuta 99999.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Do not complete any further section. Sign at 7.03 and hand the form to your supervisor.</t>
+          <t>1.13 Write the 2025 household identifier as printed on the household card, for example BAN-000123. If it cannot be established, enter 99999.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>${q1_14_result} != '1'</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>${q1_12_prev_round} = '1' and (${q1_13_prev_n} = 0 or ${q1_13_prev_id} = '')</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>regex(., '^(BAN-[0-9]{6}|99999)$')</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Tsarin bai dace ba. Misali BAN-000123, ko 99999 idan ba a sani ba.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Expected format BAN-000123, or 99999 if it cannot be established.</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -1773,12 +1781,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>s1_end</t>
+          <t>q1_13_prev_id_final</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1790,7 +1798,11 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>if(${q1_13_prev_id} != '', ${q1_13_prev_id}, ${q1_13_prev_id_other})</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -1802,32 +1814,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one result_of_visit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>s2_consent</t>
+          <t>q1_14_result</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sashe 2: Yarda</t>
+          <t>Sakamakon ziyarar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Section 2: Consent</t>
+          <t>1.14 Result of visit</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1'</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -1843,47 +1855,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>q2_01_statement_read</t>
+          <t>q1_14_stop_note</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>An karanta sanarwar yarda gaba ɗaya ga mai amsa?</t>
+          <t>Kada ka ci gaba. Aika wannan takarda yanzu, sannan ka mika na'urar ga mai kula da kai domin dubawa a 7.04.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.01 Consent statement read aloud to the respondent in full?</t>
+          <t>Do not complete any further section. Submit this form now and hand the device to your supervisor for review at 7.04.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>. = '1'</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Dole ne a karanta sanarwar yarda gaba ɗaya kafin a ci gaba.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>The consent statement must be read in full before continuing. Read it now, then record Yes.</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>${q1_14_result} != '1'</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -1896,31 +1896,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_one consent</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>q2_02_consent</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Mai amsa ya yarda da tambayoyin?</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2.02 Does the respondent consent to the household interview?</t>
-        </is>
-      </c>
+          <t>s1_end</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -1937,34 +1925,30 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one relationship</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>q2_03_relationship</t>
+          <t>s2_consent</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alaƙar mai amsa da shugaban gida</t>
+          <t>Sashe 2: Yarda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.03 Relationship of the respondent to the head of household</t>
+          <t>Section 2: Consent</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>${q2_02_consent} = '1'</t>
+          <t>${q1_14_result} = '1'</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -1982,23 +1966,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>s2_end</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>q2_01_statement_read</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>An karanta sanarwar yarda gaba ɗaya ga mai amsa?</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2.01 Consent statement read aloud to the respondent in full?</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>. = '1'</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Dole ne a karanta sanarwar yarda gaba ɗaya kafin a ci gaba.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>The consent statement must be read in full before continuing. Read it now, then record Yes.</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -2011,32 +2019,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one consent</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>s3_roster</t>
+          <t>q2_02_consent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sashe 3: Jerin mazauna gida</t>
+          <t>Mai amsa ya yarda da tambayoyin?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Section 3: Household roster</t>
+          <t>2.02 Does the respondent consent to the household interview?</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2052,22 +2060,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one relationship</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>q3_01_hh_size</t>
+          <t>q2_03_relationship</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mutane nawa ne ke zama a wannan gida?</t>
+          <t>Alaƙar mai amsa da shugaban gida</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.01 How many people usually live in this household?</t>
+          <t>2.03 Relationship of the respondent to the head of household</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2077,22 +2085,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 40</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Adadi tsakanin 1 zuwa 40. Idan ya fi haka, sanar da mai kula da kai.</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Enter between 1 and 40. If larger, notify your supervisor.</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>${q2_02_consent} = '1'</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -2105,24 +2105,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>roster</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Mazaunin gida</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Resident</t>
-        </is>
-      </c>
+          <t>s2_end</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -2134,11 +2126,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>${q3_01_hh_size}</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2146,28 +2134,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>line_no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+          <t>s3_roster</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sashe 3: Jerin mazauna gida</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Section 3: Household roster</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>position(..)</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2179,31 +2175,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>line_note</t>
+          <t>q3_01_hh_size</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Layi ${line_no}</t>
+          <t>Mutane nawa ne ke zama a wannan gida?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Line ${line_no}</t>
+          <t>3.01 How many people usually live in this household?</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Adadi tsakanin 1 zuwa 40. Idan ya fi haka, sanar da mai kula da kai.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Enter between 1 and 40. If larger, notify your supervisor.</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -2216,39 +2228,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>r_initials</t>
+          <t>roster</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baƙaƙen farko na suna</t>
+          <t>Mazaunin gida</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(2) Initials</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Baƙaƙen farko kawai, ba cikakken suna ba.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Initials only - do not record the full name.</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Resident</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -2257,7 +2257,11 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>${q3_01_hh_size}</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -2265,36 +2269,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_one relationship</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>r_relationship</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Alaƙa da shugaban gida</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>(3) Relationship to head</t>
-        </is>
-      </c>
+          <t>line_no</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>position(..)</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -2306,31 +2302,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>r_sex</t>
+          <t>line_note</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jinsi</t>
+          <t>Layi ${line_no}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(4) Sex</t>
+          <t>Line ${line_no}</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -2347,32 +2339,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>select_one age_unit</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>r_age_unit</t>
+          <t>r_initials</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shekaru ko watanni?</t>
+          <t>Baƙaƙen farko na suna</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Age recorded in years or months?</t>
+          <t>(2) Initials</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Watanni ga yara ƙasa da shekara 5.</t>
+          <t>Baƙaƙen farko kawai, ba cikakken suna ba.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Months for children under 5 years.</t>
+          <t>Initials only - do not record the full name.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2396,22 +2388,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one relationship</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>r_age_years</t>
+          <t>r_relationship</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shekaru cikakku</t>
+          <t>Alaƙa da shugaban gida</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(5) Age in completed years</t>
+          <t>(3) Relationship to head</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2421,26 +2413,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>${r_age_unit} = 'years'</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>. &gt;= 5 and . &lt;= 120</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Shekaru 5 zuwa 120. Ga yara ƙasa da 5, yi amfani da watanni.</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>5 to 120 years. For children under 5, record months instead.</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -2453,22 +2429,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>r_age_months</t>
+          <t>r_sex</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Watanni cikakku</t>
+          <t>Jinsi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(6) Age in completed months</t>
+          <t>(4) Sex</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2478,26 +2454,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>${r_age_unit} = 'months'</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 59</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Watanni 0 zuwa 59. Idan ya kai watanni 60, yi amfani da shekaru.</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0 to 59 months. At 60 months and above, record age in years.</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -2510,28 +2470,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one age_unit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>r_eligible</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>r_age_unit</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Shekaru ko watanni?</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Age recorded in years or months?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Watanni ga yara ƙasa da shekara 5.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Months for children under 5 years.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>if(${r_age_unit} = 'months' and ${r_age_months} &gt;= 9 and ${r_age_months} &lt;= 59, 1, 0)</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -2543,23 +2519,51 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>roster_end</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>r_age_years</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Shekaru cikakku</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>(5) Age in completed years</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>${r_age_unit} = 'years'</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>. &gt;= 5 and . &lt;= 120</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Shekaru 5 zuwa 120. Ga yara ƙasa da 5, yi amfani da watanni.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>5 to 120 years. For children under 5, record months instead.</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -2572,28 +2576,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>roster_count</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>r_age_months</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Watanni cikakku</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>(6) Age in completed months</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>count(${roster})</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>${r_age_unit} = 'months'</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 59</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Watanni 0 zuwa 59. Idan ya kai watanni 60, yi amfani da shekaru.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0 to 59 months. At 60 months and above, record age in years.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -2610,7 +2638,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>q3_02_eligible</t>
+          <t>r_eligible</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2624,7 +2652,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>sum(${r_eligible})</t>
+          <t>if(${r_age_unit} = 'months' and ${r_age_months} &gt;= 9 and ${r_age_months} &lt;= 59, 1, 0)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -2638,32 +2666,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>roster_mismatch_note</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>⚠ Ka ce mutane ${q3_01_hh_size} ne, amma ka rubuta ${roster_count}. Duba kafin ka ci gaba.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>⚠ You recorded ${q3_01_hh_size} usual residents but listed ${roster_count}. Check the roster before continuing.</t>
-        </is>
-      </c>
+          <t>roster_end</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>${roster_count} != ${q3_01_hh_size}</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -2679,24 +2695,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>q3_02_note</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Yara masu watanni 9-59 a wannan gida: ${q3_02_eligible}</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>3.02 Children aged 9-59 completed months in this household: ${q3_02_eligible}</t>
-        </is>
-      </c>
+          <t>roster_count</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -2704,7 +2712,11 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>count(${roster})</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -2716,12 +2728,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>s3_end</t>
+          <t>q3_02_eligible</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2733,7 +2745,11 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>sum(${r_eligible})</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -2745,22 +2761,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>roster_mismatch_note</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yaro</t>
+          <t>⚠ Ka ce mutane ${q3_01_hh_size} ne, amma ka rubuta ${roster_count}. Duba kafin ka ci gaba.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Child</t>
+          <t>⚠ You recorded ${q3_01_hh_size} usual residents but listed ${roster_count}. Check the roster before continuing.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2768,7 +2784,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1' and ${q3_02_eligible} &gt; 0</t>
+          <t>${roster_count} != ${q3_01_hh_size}</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2778,11 +2794,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>${q3_02_eligible}</t>
-        </is>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -2790,16 +2802,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>child_index</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>q3_02_note</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Yara masu watanni 9-59 a wannan gida: ${q3_02_eligible}</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3.02 Children aged 9-59 completed months in this household: ${q3_02_eligible}</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
@@ -2807,11 +2827,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>position(..)</t>
-        </is>
-      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -2823,47 +2839,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>q4_01_line</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Layin yaron a jerin mazauna</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>4.01 Line number of this child in the Section 3 roster</t>
-        </is>
-      </c>
+          <t>s3_end</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -2876,32 +2868,44 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>q4_02_initials</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Yaro</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1' and ${q3_02_eligible} &gt; 0</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>indexed-repeat(${r_initials}, ${roster}, ${q4_01_line})</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>${q3_02_eligible}</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>q4_03_age_months</t>
+          <t>child_index</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2928,7 +2932,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>indexed-repeat(${r_age_months}, ${roster}, ${q4_01_line})</t>
+          <t>position(..)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -2942,31 +2946,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>child_age_note</t>
+          <t>q4_01_line</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Watanni: ${q4_03_age_months}</t>
+          <t>Layin yaron a jerin mazauna</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.03 Age in completed months (from roster): ${q4_03_age_months}</t>
+          <t>4.01 Line number of this child in the Section 3 roster</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -2979,36 +2999,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>q4_04_sex</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Jinsin yaron</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>4.04 Sex of the child</t>
-        </is>
-      </c>
+          <t>q4_02_initials</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>indexed-repeat(${r_initials}, ${roster}, ${q4_01_line})</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
@@ -3020,36 +3032,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>select_one measured</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>q4_05_weight_status</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>An auna nauyin yaron?</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>4.05 Was the child weighed?</t>
-        </is>
-      </c>
+          <t>q4_03_age_months</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>indexed-repeat(${r_age_months}, ${roster}, ${q4_01_line})</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
@@ -3061,51 +3065,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>q4_05_weight_kg</t>
+          <t>child_age_note</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nauyi (kg)</t>
+          <t>Watanni: ${q4_03_age_months}</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.05 Weight in kg</t>
+          <t>4.03 Age in completed months (from roster): ${q4_03_age_months}</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>${q4_05_weight_status} = 'measured'</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>. &gt;= 2.0 and . &lt;= 30.0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Nauyi tsakanin 2.0 zuwa 30.0 kg.</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Weight must be between 2.0 and 30.0 kg for a child aged 9-59 months.</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -3118,32 +3102,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>weight_implausible_warn</t>
+          <t>q4_04_sex</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>⚠ Wannan nauyin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
+          <t>Jinsin yaron</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>⚠ This weight is outside the usual range for a child aged ${q4_03_age_months} months. Re-weigh to confirm, then record what you measure.</t>
+          <t>4.04 Sex of the child</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>${q4_05_weight_status} = 'measured' and (${q4_05_weight_kg} &lt; 5.0 or ${q4_05_weight_kg} &gt; 28.0)</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3164,17 +3148,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>q4_06_height_status</t>
+          <t>q4_05_weight_status</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>An auna tsayin yaron?</t>
+          <t>An auna nauyin yaron?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.06 Was the child measured?</t>
+          <t>4.05 Was the child weighed?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3205,17 +3189,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>q4_06_height_cm</t>
+          <t>q4_05_weight_kg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tsayi (cm)</t>
+          <t>Nauyi (kg)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.06 Length or height in cm</t>
+          <t>4.05 Weight in kg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3227,22 +3211,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>${q4_06_height_status} = 'measured'</t>
+          <t>${q4_05_weight_status} = 'measured'</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
+          <t>. &gt;= 2.0 and . &lt;= 30.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
+          <t>Nauyi tsakanin 2.0 zuwa 30.0 kg.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
+          <t>Weight must be between 2.0 and 30.0 kg for a child aged 9-59 months.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -3262,17 +3246,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>height_implausible_warn</t>
+          <t>weight_implausible_warn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>⚠ Wannan tsayin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
+          <t>⚠ Wannan nauyin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>⚠ This height is outside the usual range for a child aged ${q4_03_age_months} months. Re-measure to confirm, then record what you measure.</t>
+          <t>⚠ This weight is outside the usual range for a child aged ${q4_03_age_months} months. Re-weigh to confirm, then record what you measure.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3280,7 +3264,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>${q4_06_height_status} = 'measured' and (${q4_06_height_cm} &lt; 60.0 or ${q4_06_height_cm} &gt; 125.0)</t>
+          <t>${q4_05_weight_status} = 'measured' and (${q4_05_weight_kg} &lt; 5.0 or ${q4_05_weight_kg} &gt; 28.0)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3298,22 +3282,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one measure_position</t>
+          <t>select_one measured</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q4_07_position</t>
+          <t>q4_06_height_status</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yadda aka auna yaron</t>
+          <t>An auna tsayin yaron?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.07 Position in which the child was measured</t>
+          <t>4.06 Was the child measured?</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3323,11 +3307,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>${q4_06_height_status} = 'measured'</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3343,35 +3323,51 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q4_07_position_warn</t>
+          <t>q4_06_height_cm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
+          <t>Tsayi (cm)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
+          <t>4.06 Length or height in cm</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+          <t>${q4_06_height_status} = 'measured'</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>. &gt;= 45.0 and . &lt;= 130.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Tsayi tsakanin 45.0 zuwa 130.0 cm.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Height must be between 45.0 and 130.0 cm for a child aged 9-59 months.</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -3384,32 +3380,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>select_one card_seen</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>q4_08_card</t>
+          <t>height_implausible_warn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Za a iya ganin katin rigakafi na yaron?</t>
+          <t>⚠ Wannan tsayin ba kasafai ake gani ba ga yaro mai watanni ${q4_03_age_months}. Sake auna don tabbatarwa.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4.08 May I see the child's vaccination card or health record?</t>
+          <t>⚠ This height is outside the usual range for a child aged ${q4_03_age_months} months. Re-measure to confirm, then record what you measure.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>${q4_06_height_status} = 'measured' and (${q4_06_height_cm} &lt; 60.0 or ${q4_06_height_cm} &gt; 125.0)</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3425,30 +3421,34 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one document_type</t>
+          <t>select_one measure_position</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q4_08a_doc_type</t>
+          <t>q4_07_position</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wane irin takarda aka gani?</t>
+          <t>Yadda aka auna yaron</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
+          <t>4.07 Position in which the child was measured</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>${q4_08_card} = '1'</t>
+          <t>${q4_06_height_status} = 'measured'</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3466,34 +3466,30 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q4_09_measles_card</t>
+          <t>q4_07_position_warn</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>An rubuta allurar kyanda a katin?</t>
+          <t>⚠ Ana auna yara ƙasa da watanni 24 a kwance, na watanni 24 sama a tsaye.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.09 Copy from the card: is a measles dose recorded?</t>
+          <t>⚠ Convention is recumbent below 24 months and standing at 24 months and above. Confirm this was intended.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>${q4_08_card} = '1'</t>
+          <t>(${q4_03_age_months} &lt; 24 and ${q4_07_position} = '2') or (${q4_03_age_months} &gt;= 24 and ${q4_07_position} = '1')</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3511,22 +3507,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one card_seen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q4_10_measles_recall</t>
+          <t>q4_08_card</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>An taɓa yi wa yaron allurar kyanda?</t>
+          <t>Za a iya ganin katin rigakafi na yaron?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.10 Has this child ever received a measles vaccination?</t>
+          <t>4.08 May I see the child's vaccination card or health record?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3536,11 +3532,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>${q4_08_card} = '2'</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -3556,32 +3548,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one document_type</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q4_11_diarrhoea</t>
+          <t>q4_08a_doc_type</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
+          <t>Wane irin takarda aka gani?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
+          <t>4.08a Which document was seen? (addition - not on the paper form)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>${q4_08_card} = '1'</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -3597,22 +3589,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q4_12_antibiotic</t>
+          <t>q4_09_measles_card</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
+          <t>An rubuta allurar kyanda a katin?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
+          <t>4.09 Copy from the card: is a measles dose recorded?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3622,7 +3614,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>${q4_08_card} = '1'</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -3643,17 +3639,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>q4_12a_more_than_one</t>
+          <t>q4_10_measles_recall</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>An sha fiye da magani ɗaya?</t>
+          <t>An taɓa yi wa yaron allurar kyanda?</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
+          <t>4.10 Has this child ever received a measles vaccination?</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3665,7 +3661,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>${q4_12_antibiotic} = '1'</t>
+          <t>${q4_08_card} = '2'</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3683,32 +3679,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q4_13_placeholder_warning</t>
+          <t>q4_11_diarrhoea</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
+          <t>Yaron ya yi gudawa a cikin kwana 14 da suka wuce?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
+          <t>4.11 Has this child had diarrhoea in the past 14 days?</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>${q4_12_antibiotic} = '1'</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -3724,22 +3720,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>select_one_from_file medicines.csv</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q4_13_medicine</t>
+          <t>q4_12_antibiotic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wane magani aka sha?</t>
+          <t>Yaron ya sha maganin ƙwayoyin cuta a cikin kwana 30 da suka wuce?</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4.13 Which antibiotic was taken?</t>
+          <t>4.12 Has this child taken any antibiotic medicine in the past 30 days?</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3749,21 +3745,13 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>${q4_12_antibiotic} = '1'</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
@@ -3773,22 +3761,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q4_14_medicine_other</t>
+          <t>q4_12a_more_than_one</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
+          <t>An sha fiye da magani ɗaya?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.14 Write the name of the medicine as reported</t>
+          <t>4.12a Was more than one antibiotic taken? (addition - see defect C1)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3800,7 +3788,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>${q4_13_medicine} = 'OTHER96'</t>
+          <t>${q4_12_antibiotic} = '1'</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3818,31 +3806,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>q4_15_no_prescription</t>
+          <t>q4_13_placeholder_warning</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>An sami maganin ba tare da takardar likita ba?</t>
+          <t>⚠ JERIN MAGUNGUNA NA GWAJI NE - BA A YI AMFANI DA SHI A AIKI BA.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
+          <t>⚠ PLACEHOLDER MEDICINE LIST - NOT FOR DEPLOYMENT. The codelist referenced by the paper form was not supplied. See defect E1.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>${q4_12_antibiotic} = '1'</t>
@@ -3863,22 +3847,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>select_one photo_taken</t>
+          <t>select_one_from_file medicines.csv</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q4_16_photo_status</t>
+          <t>q4_13_medicine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>An ɗauki hoton kunshin maganin?</t>
+          <t>Wane magani aka sha?</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4.16 Was a photograph of the medicine packaging taken?</t>
+          <t>4.13 Which antibiotic was taken?</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3898,7 +3882,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
@@ -3908,22 +3896,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>q4_16_photo</t>
+          <t>q4_14_medicine_other</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ɗauki hoton kunshin maganin</t>
+          <t>Rubuta sunan maganin kamar yadda aka faɗa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4.16 Photograph of the medicine packaging</t>
+          <t>4.14 Write the name of the medicine as reported</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3935,7 +3923,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>${q4_16_photo_status} = '1'</t>
+          <t>${q4_13_medicine} = 'OTHER96'</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3944,11 +3932,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>max-pixels=1024</t>
-        </is>
-      </c>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -3957,28 +3941,36 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>s5_specimen</t>
+          <t>q4_15_no_prescription</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sashe 5: Tattara samfuri</t>
+          <t>An sami maganin ba tare da takardar likita ba?</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Section 5: Specimen collection</t>
+          <t>4.15 Was the medicine obtained without a prescription from a health worker?</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>${q4_12_antibiotic} = '1'</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -3994,28 +3986,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one photo_taken</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>q5_01_specimen_eligible</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+          <t>q4_16_photo_status</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>An ɗauki hoton kunshin maganin?</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4.16 Was a photograph of the medicine packaging taken?</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>${q4_12_antibiotic} = '1'</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
-        </is>
-      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -4027,30 +4031,34 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>q5_01_note</t>
+          <t>q4_16_photo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
+          <t>Ɗauki hoton kunshin maganin</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
+          <t>4.16 Photograph of the medicine packaging</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>${q5_01_specimen_eligible} = 0</t>
+          <t>${q4_16_photo_status} = '1'</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -4059,7 +4067,11 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>max-pixels=1024</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -4068,36 +4080,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>q5_02_specimen_obtained</t>
+          <t>s5_specimen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>An sami samfurin bayan gida daga yaron?</t>
+          <t>Sashe 5: Tattara samfuri</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5.02 Was a stool specimen obtained from this child?</t>
+          <t>Section 5: Specimen collection</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>${q5_01_specimen_eligible} = 1</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4113,58 +4117,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>q5_03_label_serial</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Lambar lakabin samfuri (lamba 6)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
-        </is>
-      </c>
+          <t>q5_01_specimen_eligible</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end) and count(/data/child/s5_specimen[q5_03_label_serial = current()/.]) = 1 and count(${last-saved#q5_03_label_serial}[. = current()/.]) = 0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Lambar ba ta dace ba: ko ba ta cikin kewayon ƙungiyar ka ba, ko an riga an yi amfani da ita. Duba lakabin.</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Label rejected: it is either outside your team's allocated range, already used for another child in this household, or the label used in your previous submission. Check the label book.</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>if(${q4_03_age_months} &gt;= 12, 1, 0)</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>numbers</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
@@ -4174,28 +4150,36 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>check_digit_expected</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+          <t>q5_01_note</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Yaron bai kai watanni 12 ba - ba a neman samfuri.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5.01 Child is under 12 completed months - no specimen is sought.</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>${q5_01_specimen_eligible} = 0</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
-        </is>
-      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
@@ -4207,22 +4191,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>q5_03_check_digit</t>
+          <t>q5_02_specimen_obtained</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lambar tantancewa (bayan layin)</t>
+          <t>An sami samfurin bayan gida daga yaron?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>5.03 Check character (after the hyphen)</t>
+          <t>5.02 Was a stool specimen obtained from this child?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4234,24 +4218,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
-        </is>
-      </c>
+          <t>${q5_01_specimen_eligible} = 1</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -4264,30 +4236,58 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>specimen_label_full</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+          <t>q5_03_label_serial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Lambar lakabin samfuri (lamba 6)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5.03 Specimen label serial (6 digits, after BSN)</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9]{6}$') and number(.) &gt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_start) and number(.) &lt;= number(instance('specimen_label_allocation')/root/item[team_code=${enum_team}]/range_end) and count(/data/child/s5_specimen[q5_03_label_serial = current()/.]) = 1 and count(${last-saved#q5_03_label_serial}[. = current()/.]) = 0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Lambar ba ta dace ba: ko ba ta cikin kewayon ƙungiyar ka ba, ko an riga an yi amfani da ita. Duba lakabin.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Label rejected: it is either outside your team's allocated range, already used for another child in this household, or the label used in your previous submission. Check the label book.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>numbers</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
@@ -4297,40 +4297,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q5_04_coldbox_time</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>5.04 Time the specimen was placed in the cold box</t>
-        </is>
-      </c>
+          <t>check_digit_expected</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1'</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>if((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11 = 10, 'X', string((7 * number(substr(${q5_03_label_serial},0,1)) + 6 * number(substr(${q5_03_label_serial},1,2)) + 5 * number(substr(${q5_03_label_serial},2,3)) + 4 * number(substr(${q5_03_label_serial},3,4)) + 3 * number(substr(${q5_03_label_serial},4,5)) + 2 * number(substr(${q5_03_label_serial},5,6))) mod 11))</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
@@ -4342,22 +4330,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>q5_05_coldbox_temp</t>
+          <t>q5_03_check_digit</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Zafin akwatin sanyi (°C)</t>
+          <t>Lambar tantancewa (bayan layin)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5.05 Temperature shown on the cold box thermometer</t>
+          <t>5.03 Check character (after the hyphen)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4374,17 +4362,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
+          <t>translate(., 'x', 'X') = ${check_digit_expected}</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
+          <t>Lambar tantancewa ba ta dace ba. Sake duba lambobin lakabin.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Temperature must be between -20.0 and 40.0 °C.</t>
+          <t>Check character does not match the serial. Re-read the label - two digits may have been swapped.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -4399,36 +4387,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>q5_05_temp_warn</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
-        </is>
-      </c>
+          <t>specimen_label_full</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>concat('BSN', ${q5_03_label_serial}, '-', translate(${q5_03_check_digit}, 'x', 'X'))</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
@@ -4440,22 +4420,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>select_one no_specimen_reason</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>q5_06_reason</t>
+          <t>q5_04_coldbox_time</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dalilin da ya sa ba a sami samfuri ba</t>
+          <t>Lokacin da aka sanya samfurin cikin akwatin sanyi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5.06 Reason no specimen was obtained</t>
+          <t>5.04 Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4467,7 +4447,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>${q5_02_specimen_obtained} = '2'</t>
+          <t>${q5_02_specimen_obtained} = '1'</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4485,22 +4465,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>q5_07_reason_other</t>
+          <t>q5_05_coldbox_temp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bayyana dalilin</t>
+          <t>Zafin akwatin sanyi (°C)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5.07 Specify</t>
+          <t>5.05 Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -4512,12 +4492,24 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>${q5_06_reason} = '96'</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+          <t>${q5_02_specimen_obtained} = '1'</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>. &gt;= -20.0 and . &lt;= 40.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Zafi tsakanin -20.0 zuwa 40.0 °C.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Temperature must be between -20.0 and 40.0 °C.</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
@@ -4530,20 +4522,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>s5_end</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+          <t>q5_05_temp_warn</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>⚠ Zafin ya fita daga 2-8 °C. Sanar da mai kula da kai yanzu.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>⚠ Temperature is outside 2-8 °C. Report to your supervisor now - the cold chain may have failed.</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '1' and (${q5_05_coldbox_temp} &lt; 2 or ${q5_05_coldbox_temp} &gt; 8)</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -4559,20 +4563,36 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>select_one no_specimen_reason</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>child_end</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+          <t>q5_06_reason</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dalilin da ya sa ba a sami samfuri ba</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5.06 Reason no specimen was obtained</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>${q5_02_specimen_obtained} = '2'</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -4588,30 +4608,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>s6_environment</t>
+          <t>q5_07_reason_other</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sashe 6: Yanayin gida</t>
+          <t>Bayyana dalilin</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Section 6: Household environment</t>
+          <t>5.07 Specify</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+          <t>${q5_06_reason} = '96'</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4629,31 +4653,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one water_source</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>q6_01_water</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>6.01 What is the main source of drinking water for this household?</t>
-        </is>
-      </c>
+          <t>s5_end</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
@@ -4670,31 +4682,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>q6_02_toilet</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>6.02 What kind of toilet facility do members of this household use?</t>
-        </is>
-      </c>
+          <t>child_end</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -4711,32 +4711,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>q6_03_livestock</t>
+          <t>s6_environment</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
+          <t>Sashe 6: Yanayin gida</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
+          <t>Section 6: Household environment</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>${q1_14_result} = '1' and ${q2_02_consent} = '1'</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4752,22 +4752,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one water_source</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>q6_04_animal_antibiotic</t>
+          <t>q6_01_water</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
+          <t>Babbar hanyar samun ruwan sha ta wannan gida?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.01 What is the main source of drinking water for this household?</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4777,11 +4777,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>${q6_03_livestock} = '1'</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -4797,22 +4793,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>select_one handwashing</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>q6_05_handwashing</t>
+          <t>q6_02_toilet</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
+          <t>Wane irin bandaki wannan gida ke amfani da shi?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
+          <t>6.02 What kind of toilet facility do members of this household use?</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4838,22 +4834,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>q6_06_hh_diarrhoea</t>
+          <t>q6_03_livestock</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
+          <t>Ana kiwon dabbobi ko kaji a cikin gidan?</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.03 Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4879,22 +4875,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>select_multiple assets</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>q6_07_assets</t>
+          <t>q6_04_animal_antibiotic</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+          <t>An ba dabbobin maganin ƙwayoyin cuta cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6.07 Which of the following does this household own?</t>
+          <t>6.04 Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4904,22 +4900,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be selected together with any other item.</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>${q6_03_livestock} = '1'</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
@@ -4932,19 +4920,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one handwashing</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>s6_end</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+          <t>q6_05_handwashing</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Duba: akwai wurin wanke hannu da sabulu da ruwa?</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>6.05 Observe: is there a handwashing station with both soap and water?</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -4961,27 +4961,31 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>s7_closeout</t>
+          <t>q6_06_hh_diarrhoea</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sashe 7: Kammalawa</t>
+          <t>Wani a wannan gida ya yi gudawa cikin makonni biyu da suka wuce?</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Section 7: Close-out and supervisor review</t>
+          <t>6.06 Has any member of this household had diarrhoea in the past two weeks?</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -4998,28 +5002,48 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_multiple assets</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>interview_duration_min</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+          <t>q6_07_assets</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Waɗanne daga cikin waɗannan wannan gida ke da su?</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>6.07 Which of the following does this household own?</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>not(selected(., 'H') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Ba za a iya zaɓar 'Babu ɗaya daga cikin waɗannan' tare da wasu ba.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be selected together with any other item.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
@@ -5031,24 +5055,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>q7_02_observation</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Duk wani abin lura da zai taimaka wa ofis</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>7.02 Record any observation that may help the office interpret this form</t>
-        </is>
-      </c>
+          <t>s6_end</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -5058,11 +5074,7 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
@@ -5072,22 +5084,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>select_one_from_file staff_roster.csv</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>q7_04_supervisor</t>
+          <t>s7_closeout</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lambar mai kula</t>
+          <t>Sashe 7: Kammalawa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7.04 Supervisor code</t>
+          <t>Section 7: Close-out and supervisor review</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5098,16 +5110,8 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>role='Team supervisor'</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
@@ -5117,36 +5121,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>select_one supervisor_decision</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>q7_05_supervisor_decision</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Shawarar mai kula kan wannan takarda</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>7.05 Supervisor decision on this form</t>
-        </is>
-      </c>
+          <t>interview_duration_min</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>${q7_04_supervisor} != ''</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>round((decimal-date-time(${end_time}) - decimal-date-time(${start_time})) * 1440, 1)</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
@@ -5158,16 +5154,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>s7_end</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+          <t>q7_02_observation</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Duk wani abin lura da zai taimaka wa ofis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>7.02 Record any observation that may help the office interpret this form</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -5177,12 +5181,131 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>select_one_from_file staff_roster.csv</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>q7_04_supervisor</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Lambar mai kula</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>7.04 Supervisor code</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>role='Team supervisor'</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>select_one supervisor_decision</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>q7_05_supervisor_decision</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Shawarar mai kula kan wannan takarda</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>7.05 Supervisor decision on this form</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>${q7_04_supervisor} != ''</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>s7_end</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6868,7 +6991,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026063001</t>
+          <t>20260630-9c5d68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/part2_q3/form/bansara_hh_2026.xlsx
+++ b/part2_q3/form/bansara_hh_2026.xlsx
@@ -624,7 +624,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>'20260630-9c5d68'</t>
+          <t>'20260630-24d842'</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2974,17 +2974,17 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1</t>
+          <t>. &gt;= 1 and . &lt;= ${roster_count} and indexed-repeat(${r_eligible}, ${roster}, .) = 1 and count(/data/child[q4_01_line = current()/.]) = 1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Wannan layin ba yaro mai watanni 9-59 ba ne. Duba jerin.</t>
+          <t>Layin ba daidai ba ne: dole ya zama yaro mai watanni 9-59 da ba a riga an rubuta shi ba a wani sashe.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>That line is not a child aged 9-59 completed months. Check the roster.</t>
+          <t>Invalid line: it must be a child aged 9-59 completed months who has not already been recorded in another child module.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260630-9c5d68</t>
+          <t>20260630-24d842</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
